--- a/internal_doc/03.开发设计/OM_Agent接口.xlsx
+++ b/internal_doc/03.开发设计/OM_Agent接口.xlsx
@@ -182,199 +182,199 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>2、是否能ssh登陆</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3、获取hostname</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、是否ping得通</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>扫描选中的host</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>intallRemoteAgent</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{ip,isInstall:true/false,transctionID:1313},...]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、检测remote_agent是否已启动</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2、把安装包发到远端机器</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3、启动romote_agent</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4、检测romote_agent是否已启动</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>([{ip,usrname, password,local_pack_and_conf_file,romote_ip,remote_pack_path},...])</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>获取remote_host_info</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>getHostInfo</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>([{ip,usrname,password},...])</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>removeRemoteAgent</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>（[{ip/hostname,usrname, password},...]）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>([{ip,transctionID},...])</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{OAIsRemove:true/false},...]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>检测系统是否注册OMAgent服务</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>检测OMAgent是否在运行</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>从系统中删除OMAgent服务</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>配置host</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>与OMServer接口</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>([{ip,usrname, password},...])</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>添加远端公钥到本地authorized_keys文件中</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{isBuild:true/false,transctionID:34532}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>([{ip,[{ip:hostname,...}]},...])</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>installSvc</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>regHosts</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>buildRelations</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>startSvc</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>scan host</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>启动进程命令</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3、检测CPU（型号，核数，主频）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4、检测内存（型号，总大小，剩余大小）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2、检测os版本（版本）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5、检测磁盘（名称，mount路径，总大小,剩余大小）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6、检测网卡（型号，个数，带宽）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7、检测关键端口（）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>检测端口状态</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>操作系统信息获取（见gethostinfo）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>testSvc</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>发送一个业务请求</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10、ip table（开或关）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8、检测依赖软件包和服务信息（版本，服务是否已启动)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9、检测是否已经安装om(检测OM安装包和安装路径）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、取hosts文件内容返回</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{[ip:"",name:"x86-1",os:"",cpu:[],men:[],disk:[],net:[],port:[],servic:[],hasInstall[],ipTable],...}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>[{ip:134,hostname:"ubuntu-dev1",canPing:true/false, canSsh:true/false},...]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2、是否能ssh登陆</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3、获取hostname</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、是否ping得通</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>扫描选中的host</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>intallRemoteAgent</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{ip,isInstall:true/false,transctionID:1313},...]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、检测remote_agent是否已启动</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2、把安装包发到远端机器</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3、启动romote_agent</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4、检测romote_agent是否已启动</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>([{ip,usrname, password,local_pack_and_conf_file,romote_ip,remote_pack_path},...])</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>获取remote_host_info</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>getHostInfo</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>([{ip,usrname,password},...])</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>removeRemoteAgent</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>（[{ip/hostname,usrname, password},...]）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>([{ip,transctionID},...])</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{OAIsRemove:true/false},...]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>检测系统是否注册OMAgent服务</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>检测OMAgent是否在运行</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>从系统中删除OMAgent服务</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>配置host</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>与OMServer接口</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>([{ip,usrname, password},...])</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>添加远端公钥到本地authorized_keys文件中</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{isBuild:true/false,transctionID:34532}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>([{ip,[{ip:hostname,...}]},...])</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>installSvc</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>regHosts</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>buildRelations</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>startSvc</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>scan host</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>启动进程命令</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3、检测CPU（型号，核数，主频）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4、检测内存（型号，总大小，剩余大小）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2、检测os版本（版本）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>5、检测磁盘（名称，mount路径，总大小,剩余大小）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>6、检测网卡（型号，个数，带宽）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>7、检测关键端口（）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>检测端口状态</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>操作系统信息获取（见gethostinfo）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>testSvc</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>发送一个业务请求</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10、ip table（开或关）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>8、检测依赖软件包和服务信息（版本，服务是否已启动)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>9、检测是否已经安装om(检测OM安装包和安装路径）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、取hosts文件内容返回</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{[ip:"",name:"x86-1",os:"",cpu:[],men:[],disk:[],net:[],port:[],servic:[],hasInstall[],ipTable],...}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -458,6 +458,74 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -469,7 +537,7 @@
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr val="window" lastClr="C7EDCC"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -765,7 +833,7 @@
         <v>39</v>
       </c>
       <c r="E1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F1" t="s">
         <v>5</v>
@@ -790,26 +858,26 @@
         <v>38</v>
       </c>
       <c r="E9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G9" t="s">
-        <v>41</v>
+        <v>89</v>
       </c>
       <c r="H9" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="H10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="H11" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -817,7 +885,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E19" t="s">
         <v>40</v>
@@ -828,78 +896,78 @@
         <v>3</v>
       </c>
       <c r="E21" t="s">
+        <v>45</v>
+      </c>
+      <c r="F21" t="s">
+        <v>51</v>
+      </c>
+      <c r="G21" t="s">
         <v>46</v>
       </c>
-      <c r="F21" t="s">
-        <v>52</v>
-      </c>
-      <c r="G21" t="s">
+      <c r="H21" t="s">
         <v>47</v>
-      </c>
-      <c r="H21" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="22" spans="1:8">
       <c r="H22" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="23" spans="1:8">
       <c r="H23" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="24" spans="1:8">
       <c r="H24" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="26" spans="1:8">
       <c r="C26" t="s">
+        <v>52</v>
+      </c>
+      <c r="E26" t="s">
         <v>53</v>
       </c>
-      <c r="E26" t="s">
+      <c r="F26" t="s">
         <v>54</v>
       </c>
-      <c r="F26" t="s">
-        <v>55</v>
-      </c>
       <c r="G26" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H26" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="27" spans="1:8">
       <c r="H27" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="28" spans="1:8">
       <c r="H28" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="29" spans="1:8">
       <c r="H29" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="30" spans="1:8">
       <c r="H30" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="31" spans="1:8">
       <c r="H31" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="32" spans="1:8">
       <c r="H32" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="33" spans="3:8">
@@ -919,17 +987,17 @@
     </row>
     <row r="36" spans="3:8">
       <c r="H36" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="37" spans="3:8">
       <c r="H37" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="38" spans="3:8">
       <c r="H38" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="41" spans="3:8">
@@ -937,21 +1005,21 @@
         <v>11</v>
       </c>
       <c r="E41" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F41" t="s">
+        <v>57</v>
+      </c>
+      <c r="G41" t="s">
         <v>58</v>
       </c>
-      <c r="G41" t="s">
+      <c r="H41" s="1" t="s">
         <v>59</v>
-      </c>
-      <c r="H41" s="1" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="42" spans="3:8">
       <c r="H42" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="43" spans="3:8">
@@ -976,12 +1044,12 @@
     </row>
     <row r="47" spans="3:8">
       <c r="H47" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="51" spans="1:8">
       <c r="A51" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C51" t="s">
         <v>3</v>
@@ -996,13 +1064,13 @@
         <v>16</v>
       </c>
       <c r="E53" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F53" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G53" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="H53" t="s">
         <v>18</v>
@@ -1020,7 +1088,7 @@
     </row>
     <row r="56" spans="1:8">
       <c r="H56" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="57" spans="1:8">
@@ -1037,10 +1105,10 @@
         <v>17</v>
       </c>
       <c r="E60" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F60" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="H60" t="s">
         <v>21</v>
@@ -1059,7 +1127,7 @@
         <v>23</v>
       </c>
       <c r="E69" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F69" t="s">
         <v>24</v>
@@ -1086,7 +1154,7 @@
         <v>27</v>
       </c>
       <c r="E74" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F74" t="s">
         <v>28</v>
@@ -1113,7 +1181,7 @@
         <v>33</v>
       </c>
       <c r="E78" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F78" t="s">
         <v>35</v>
@@ -1122,7 +1190,7 @@
         <v>34</v>
       </c>
       <c r="H78" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
   </sheetData>
@@ -1164,17 +1232,17 @@
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>

--- a/internal_doc/03.开发设计/OM_Agent接口.xlsx
+++ b/internal_doc/03.开发设计/OM_Agent接口.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="91">
   <si>
     <t>检测host</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -222,55 +222,143 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>获取remote_host_info</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>getHostInfo</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>([{ip,usrname,password},...])</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>removeRemoteAgent</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>([{ip,transctionID},...])</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{OAIsRemove:true/false},...]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>检测系统是否注册OMAgent服务</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>检测OMAgent是否在运行</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>从系统中删除OMAgent服务</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>配置host</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>与OMServer接口</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>添加远端公钥到本地authorized_keys文件中</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>installSvc</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>regHosts</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>buildRelations</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>startSvc</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>scan host</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>启动进程命令</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3、检测CPU（型号，核数，主频）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4、检测内存（型号，总大小，剩余大小）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2、检测os版本（版本）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5、检测磁盘（名称，mount路径，总大小,剩余大小）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6、检测网卡（型号，个数，带宽）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7、检测关键端口（）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>检测端口状态</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>操作系统信息获取（见gethostinfo）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>testSvc</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>发送一个业务请求</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10、ip table（开或关）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8、检测依赖软件包和服务信息（版本，服务是否已启动)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9、检测是否已经安装om(检测OM安装包和安装路径）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、取hosts文件内容返回</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>（[{ip/hostname,usrname, password},...]）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>([{ip,usrname, password,local_pack_and_conf_file,romote_ip,remote_pack_path},...])</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>获取remote_host_info</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>getHostInfo</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>([{ip,usrname,password},...])</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>removeRemoteAgent</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>（[{ip/hostname,usrname, password},...]）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>([{ip,transctionID},...])</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{OAIsRemove:true/false},...]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>检测系统是否注册OMAgent服务</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>检测OMAgent是否在运行</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>从系统中删除OMAgent服务</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>配置host</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>与OMServer接口</t>
+    <t>{[ip:"",name:"x86-1",os:"",cpu:[],men:[],disk:[],net:[],port:[],servic:[],hasInstall[],ipTable],...}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -278,7 +366,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>添加远端公钥到本地authorized_keys文件中</t>
+    <t>([{ip,[{ip:hostname,...}]},...])</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>安装remote_agent</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -286,95 +378,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>([{ip,[{ip:hostname,...}]},...])</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>installSvc</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>regHosts</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>buildRelations</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>startSvc</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>scan host</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>启动进程命令</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3、检测CPU（型号，核数，主频）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4、检测内存（型号，总大小，剩余大小）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2、检测os版本（版本）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>5、检测磁盘（名称，mount路径，总大小,剩余大小）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>6、检测网卡（型号，个数，带宽）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>7、检测关键端口（）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>检测端口状态</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>操作系统信息获取（见gethostinfo）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>testSvc</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>发送一个业务请求</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10、ip table（开或关）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>8、检测依赖软件包和服务信息（版本，服务是否已启动)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>9、检测是否已经安装om(检测OM安装包和安装路径）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、取hosts文件内容返回</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{[ip:"",name:"x86-1",os:"",cpu:[],men:[],disk:[],net:[],port:[],servic:[],hasInstall[],ipTable],...}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{ip:134,hostname:"ubuntu-dev1",canPing:true/false, canSsh:true/false},...]</t>
+    <t>{rc:SDB_OK,[{ip:134,hostname:"ubuntu-dev1",canPing:true/false, canSsh:true/false},...]}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -819,7 +823,7 @@
   <cols>
     <col min="1" max="1" width="14.5" customWidth="1"/>
     <col min="3" max="3" width="16.375" customWidth="1"/>
-    <col min="5" max="5" width="16.5" customWidth="1"/>
+    <col min="5" max="5" width="19.375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="21.25" customWidth="1"/>
     <col min="7" max="7" width="65.375" customWidth="1"/>
     <col min="8" max="8" width="57.375" customWidth="1"/>
@@ -833,7 +837,7 @@
         <v>39</v>
       </c>
       <c r="E1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F1" t="s">
         <v>5</v>
@@ -858,13 +862,13 @@
         <v>38</v>
       </c>
       <c r="E9" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="F9" t="s">
-        <v>56</v>
+        <v>83</v>
       </c>
       <c r="G9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H9" t="s">
         <v>43</v>
@@ -899,7 +903,7 @@
         <v>45</v>
       </c>
       <c r="F21" t="s">
-        <v>51</v>
+        <v>84</v>
       </c>
       <c r="G21" t="s">
         <v>46</v>
@@ -925,49 +929,49 @@
     </row>
     <row r="26" spans="1:8">
       <c r="C26" t="s">
+        <v>51</v>
+      </c>
+      <c r="E26" t="s">
         <v>52</v>
       </c>
-      <c r="E26" t="s">
+      <c r="F26" t="s">
         <v>53</v>
       </c>
-      <c r="F26" t="s">
-        <v>54</v>
-      </c>
       <c r="G26" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="H26" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
     </row>
     <row r="27" spans="1:8">
       <c r="H27" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
     </row>
     <row r="28" spans="1:8">
       <c r="H28" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
     </row>
     <row r="29" spans="1:8">
       <c r="H29" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
     </row>
     <row r="30" spans="1:8">
       <c r="H30" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
     </row>
     <row r="31" spans="1:8">
       <c r="H31" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
     </row>
     <row r="32" spans="1:8">
       <c r="H32" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="33" spans="3:8">
@@ -987,17 +991,17 @@
     </row>
     <row r="36" spans="3:8">
       <c r="H36" s="4" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
     </row>
     <row r="37" spans="3:8">
       <c r="H37" s="4" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
     </row>
     <row r="38" spans="3:8">
       <c r="H38" s="4" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
     </row>
     <row r="41" spans="3:8">
@@ -1005,21 +1009,21 @@
         <v>11</v>
       </c>
       <c r="E41" t="s">
+        <v>54</v>
+      </c>
+      <c r="F41" t="s">
         <v>55</v>
       </c>
-      <c r="F41" t="s">
+      <c r="G41" t="s">
+        <v>56</v>
+      </c>
+      <c r="H41" s="1" t="s">
         <v>57</v>
-      </c>
-      <c r="G41" t="s">
-        <v>58</v>
-      </c>
-      <c r="H41" s="1" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="42" spans="3:8">
       <c r="H42" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="43" spans="3:8">
@@ -1044,15 +1048,15 @@
     </row>
     <row r="47" spans="3:8">
       <c r="H47" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="51" spans="1:8">
       <c r="A51" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C51" t="s">
-        <v>3</v>
+        <v>88</v>
       </c>
       <c r="H51" s="1"/>
     </row>
@@ -1064,13 +1068,13 @@
         <v>16</v>
       </c>
       <c r="E53" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="F53" t="s">
-        <v>64</v>
+        <v>86</v>
       </c>
       <c r="G53" t="s">
-        <v>66</v>
+        <v>89</v>
       </c>
       <c r="H53" t="s">
         <v>18</v>
@@ -1088,7 +1092,7 @@
     </row>
     <row r="56" spans="1:8">
       <c r="H56" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="57" spans="1:8">
@@ -1105,10 +1109,10 @@
         <v>17</v>
       </c>
       <c r="E60" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="F60" t="s">
-        <v>67</v>
+        <v>87</v>
       </c>
       <c r="H60" t="s">
         <v>21</v>
@@ -1127,7 +1131,7 @@
         <v>23</v>
       </c>
       <c r="E69" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="F69" t="s">
         <v>24</v>
@@ -1154,7 +1158,7 @@
         <v>27</v>
       </c>
       <c r="E74" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="F74" t="s">
         <v>28</v>
@@ -1181,7 +1185,7 @@
         <v>33</v>
       </c>
       <c r="E78" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="F78" t="s">
         <v>35</v>
@@ -1190,7 +1194,7 @@
         <v>34</v>
       </c>
       <c r="H78" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -1232,17 +1236,17 @@
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="3" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>

--- a/internal_doc/03.开发设计/OM_Agent接口.xlsx
+++ b/internal_doc/03.开发设计/OM_Agent接口.xlsx
@@ -4,19 +4,21 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14385" windowHeight="7485"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14385" windowHeight="7485" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="与OMSvc接口" sheetId="2" r:id="rId1"/>
     <sheet name="内部接口" sheetId="3" r:id="rId2"/>
     <sheet name="底层提供" sheetId="4" r:id="rId3"/>
+    <sheet name="问题" sheetId="5" r:id="rId4"/>
+    <sheet name="Sheet2" sheetId="6" r:id="rId5"/>
   </sheets>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="93">
   <si>
     <t>检测host</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -378,7 +380,15 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>{rc:SDB_OK,[{ip:134,hostname:"ubuntu-dev1",canPing:true/false, canSsh:true/false},...]}</t>
+    <t>{rc:SDB_OK,[{ip:134,hostname:"ubuntu-dev1",canPing:true/false, canSsh:true/false, rc:SDB_OK},...]}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ssh没开启，返回结果不够准确。reval is: { "": { "Ping": true, "Ssh": false, "HostName": null, "Rc": -10, "Detail": "{ \"ErrMsg\": \"Authentication failed (username/password)\" }" } }</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>部分机器ssh功能已开启，但通过new Ssh()连不上</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -462,74 +472,6 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -541,7 +483,7 @@
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="C7EDCC"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -824,8 +766,8 @@
     <col min="1" max="1" width="14.5" customWidth="1"/>
     <col min="3" max="3" width="16.375" customWidth="1"/>
     <col min="5" max="5" width="19.375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="21.25" customWidth="1"/>
-    <col min="7" max="7" width="65.375" customWidth="1"/>
+    <col min="6" max="6" width="29" customWidth="1"/>
+    <col min="7" max="7" width="69.25" customWidth="1"/>
     <col min="8" max="8" width="57.375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1253,4 +1195,40 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
+  <cols>
+    <col min="1" max="1" width="46.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetData/>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+</worksheet>
 </file>
--- a/internal_doc/03.开发设计/OM_Agent接口.xlsx
+++ b/internal_doc/03.开发设计/OM_Agent接口.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14385" windowHeight="7485" activeTab="4"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14385" windowHeight="7485" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="与OMSvc接口" sheetId="2" r:id="rId1"/>
@@ -12,13 +12,14 @@
     <sheet name="底层提供" sheetId="4" r:id="rId3"/>
     <sheet name="问题" sheetId="5" r:id="rId4"/>
     <sheet name="Sheet2" sheetId="6" r:id="rId5"/>
+    <sheet name="Sheet1" sheetId="7" r:id="rId6"/>
   </sheets>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="105">
   <si>
     <t>检测host</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -88,87 +89,339 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>检测本地是否存在公秘钥，若无则生成</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>登陆remote_agent,检测远端是否存在公秘钥，若无则生成</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>添加本地公钥到远端authorized_keys文件中</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>循环检测远端机器的hosts文件是否已包含其他几台机器的hostname</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>若ping hostname不通，则添加该hostname 和 ip 到hosts文件中</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>安装服务</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>（ip,{安装配置参数}）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{install:true/false,errmsg:{},transctionID:34324}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>检测安装配置参数合法性</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>启动服务</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>（ip,{启动配置参数}）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>检测启动配置参数合法性</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{startSvc:true/false,errmsg:{},tranctionID:1233}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>检测服务是否安装成功</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>检测服务是否成功启动</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{succeed:true/false}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>({coord_ip,sdb_path})</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>阶段</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>创建cluster</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>扫描host</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>事件</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>scanHost</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2、是否能ssh登陆</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3、获取hostname</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、是否ping得通</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>扫描选中的host</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>intallRemoteAgent</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{ip,isInstall:true/false,transctionID:1313},...]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、检测remote_agent是否已启动</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2、把安装包发到远端机器</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3、启动romote_agent</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4、检测romote_agent是否已启动</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>获取remote_host_info</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>getHostInfo</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>([{ip,usrname,password},...])</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>removeRemoteAgent</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>([{ip,transctionID},...])</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{OAIsRemove:true/false},...]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>检测系统是否注册OMAgent服务</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>检测OMAgent是否在运行</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>从系统中删除OMAgent服务</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>配置host</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>与OMServer接口</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>添加远端公钥到本地authorized_keys文件中</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>installSvc</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>regHosts</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>buildRelations</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>startSvc</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>scan host</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>启动进程命令</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3、检测CPU（型号，核数，主频）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4、检测内存（型号，总大小，剩余大小）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2、检测os版本（版本）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5、检测磁盘（名称，mount路径，总大小,剩余大小）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6、检测网卡（型号，个数，带宽）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7、检测关键端口（）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>检测端口状态</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>操作系统信息获取（见gethostinfo）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>testSvc</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>发送一个业务请求</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10、ip table（开或关）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8、检测依赖软件包和服务信息（版本，服务是否已启动)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9、检测是否已经安装om(检测OM安装包和安装路径）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、取hosts文件内容返回</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>([{ip,usrname, password,local_pack_and_conf_file,romote_ip,remote_pack_path},...])</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{[ip:"",name:"x86-1",os:"",cpu:[],men:[],disk:[],net:[],port:[],servic:[],hasInstall[],ipTable],...}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>([{ip,usrname, password},...])</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>([{ip,[{ip:hostname,...}]},...])</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>安装remote_agent</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{isBuild:true/false,transctionID:34532}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{rc:SDB_OK,[{ip:134,hostname:"ubuntu-dev1",canPing:true/false, canSsh:true/false, rc:SDB_OK},...]}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ssh没开启，返回结果不够准确。reval is: { "": { "Ping": true, "Ssh": false, "HostName": null, "Rc": -10, "Detail": "{ \"ErrMsg\": \"Authentication failed (username/password)\" }" } }</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>部分机器ssh功能已开启，但通过new Ssh()连不上</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>basic check</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{HostInfo:[{IP/HostName,User, Passwd, SshPort, AgentPort},...]}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>check host</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{User, Passwd}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>发给远程 Agent</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>发给本地Agent，由本地Agent转发</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>注册hosts</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>检测本地是否存在公秘钥，若无则生成</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>登陆remote_agent,检测远端是否存在公秘钥，若无则生成</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>添加本地公钥到远端authorized_keys文件中</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>循环检测远端机器的hosts文件是否已包含其他几台机器的hostname</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>若ping hostname不通，则添加该hostname 和 ip 到hosts文件中</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>安装服务</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>（ip,{安装配置参数}）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{install:true/false,errmsg:{},transctionID:34324}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>检测安装配置参数合法性</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>启动服务</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>（ip,{启动配置参数}）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>检测启动配置参数合法性</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{startSvc:true/false,errmsg:{},tranctionID:1233}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>检测服务是否安装成功</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>检测服务是否成功启动</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>服务测试</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>{succeed:true/false}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>({coord_ip,sdb_path})</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>阶段</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>创建cluster</t>
+    <t>检测host</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>命令</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>命令字</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -176,219 +429,15 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>事件</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>scanHost</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2、是否能ssh登陆</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3、获取hostname</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、是否ping得通</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>扫描选中的host</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>intallRemoteAgent</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{ip,isInstall:true/false,transctionID:1313},...]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、检测remote_agent是否已启动</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2、把安装包发到远端机器</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3、启动romote_agent</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4、检测romote_agent是否已启动</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>获取remote_host_info</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>getHostInfo</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>([{ip,usrname,password},...])</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>removeRemoteAgent</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>([{ip,transctionID},...])</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{OAIsRemove:true/false},...]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>检测系统是否注册OMAgent服务</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>检测OMAgent是否在运行</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>从系统中删除OMAgent服务</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>配置host</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>与OMServer接口</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>添加远端公钥到本地authorized_keys文件中</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>installSvc</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>regHosts</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>buildRelations</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>startSvc</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>scan host</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>启动进程命令</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3、检测CPU（型号，核数，主频）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4、检测内存（型号，总大小，剩余大小）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2、检测os版本（版本）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>5、检测磁盘（名称，mount路径，总大小,剩余大小）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>6、检测网卡（型号，个数，带宽）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>7、检测关键端口（）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>检测端口状态</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>操作系统信息获取（见gethostinfo）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>testSvc</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>发送一个业务请求</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10、ip table（开或关）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>8、检测依赖软件包和服务信息（版本，服务是否已启动)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>9、检测是否已经安装om(检测OM安装包和安装路径）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、取hosts文件内容返回</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>（[{ip/hostname,usrname, password},...]）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>([{ip,usrname, password,local_pack_and_conf_file,romote_ip,remote_pack_path},...])</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{[ip:"",name:"x86-1",os:"",cpu:[],men:[],disk:[],net:[],port:[],servic:[],hasInstall[],ipTable],...}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>([{ip,usrname, password},...])</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>([{ip,[{ip:hostname,...}]},...])</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>安装remote_agent</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{isBuild:true/false,transctionID:34532}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{rc:SDB_OK,[{ip:134,hostname:"ubuntu-dev1",canPing:true/false, canSsh:true/false, rc:SDB_OK},...]}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ssh没开启，返回结果不够准确。reval is: { "": { "Ping": true, "Ssh": false, "HostName": null, "Rc": -10, "Detail": "{ \"ErrMsg\": \"Authentication failed (username/password)\" }" } }</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>部分机器ssh功能已开启，但通过new Ssh()连不上</t>
+    <t>参数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>响应</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"rc":SDB_OK,HostInfo:{[{ip:134,hostname:"ubuntu-dev1",canPing:true/false, canSsh:true/false, rc:SDB_OK},...]}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -460,18 +509,89 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -483,7 +603,7 @@
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr val="window" lastClr="C7EDCC"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -766,22 +886,22 @@
     <col min="1" max="1" width="14.5" customWidth="1"/>
     <col min="3" max="3" width="16.375" customWidth="1"/>
     <col min="5" max="5" width="19.375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="29" customWidth="1"/>
-    <col min="7" max="7" width="69.25" customWidth="1"/>
+    <col min="6" max="6" width="35.875" style="5" customWidth="1"/>
+    <col min="7" max="7" width="34.625" customWidth="1"/>
     <col min="8" max="8" width="57.375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E1" t="s">
-        <v>61</v>
-      </c>
-      <c r="F1" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
       <c r="G1" t="s">
@@ -793,37 +913,59 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="27">
       <c r="A9" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C9" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E9" t="s">
-        <v>67</v>
-      </c>
-      <c r="F9" t="s">
-        <v>83</v>
+        <v>65</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>91</v>
       </c>
       <c r="G9" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="H9" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="H10" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="H11" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="27">
+      <c r="E13" t="s">
+        <v>90</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="H13" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="E16" t="s">
+        <v>92</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="H16" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -831,89 +973,89 @@
         <v>0</v>
       </c>
       <c r="C19" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E19" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="54">
       <c r="C21" t="s">
         <v>3</v>
       </c>
       <c r="E21" t="s">
+        <v>43</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="G21" t="s">
+        <v>44</v>
+      </c>
+      <c r="H21" t="s">
         <v>45</v>
-      </c>
-      <c r="F21" t="s">
-        <v>84</v>
-      </c>
-      <c r="G21" t="s">
-        <v>46</v>
-      </c>
-      <c r="H21" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="22" spans="1:8">
       <c r="H22" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="23" spans="1:8">
       <c r="H23" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="24" spans="1:8">
       <c r="H24" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="27">
+      <c r="C26" t="s">
+        <v>49</v>
+      </c>
+      <c r="E26" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="26" spans="1:8">
-      <c r="C26" t="s">
+      <c r="F26" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="E26" t="s">
-        <v>52</v>
-      </c>
-      <c r="F26" t="s">
-        <v>53</v>
-      </c>
       <c r="G26" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="H26" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="27" spans="1:8">
       <c r="H27" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="28" spans="1:8">
       <c r="H28" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="29" spans="1:8">
       <c r="H29" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="30" spans="1:8">
       <c r="H30" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="31" spans="1:8">
       <c r="H31" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="32" spans="1:8">
       <c r="H32" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="33" spans="3:8">
@@ -933,17 +1075,17 @@
     </row>
     <row r="36" spans="3:8">
       <c r="H36" s="4" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="37" spans="3:8">
       <c r="H37" s="4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="38" spans="3:8">
       <c r="H38" s="4" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="41" spans="3:8">
@@ -951,21 +1093,21 @@
         <v>11</v>
       </c>
       <c r="E41" t="s">
+        <v>52</v>
+      </c>
+      <c r="F41" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="G41" t="s">
         <v>54</v>
       </c>
-      <c r="F41" t="s">
+      <c r="H41" s="1" t="s">
         <v>55</v>
-      </c>
-      <c r="G41" t="s">
-        <v>56</v>
-      </c>
-      <c r="H41" s="1" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="42" spans="3:8">
       <c r="H42" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="43" spans="3:8">
@@ -990,51 +1132,51 @@
     </row>
     <row r="47" spans="3:8">
       <c r="H47" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="51" spans="1:8">
       <c r="A51" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C51" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="H51" s="1"/>
     </row>
     <row r="52" spans="1:8">
       <c r="H52" s="1"/>
     </row>
-    <row r="53" spans="1:8">
+    <row r="53" spans="1:8" ht="27">
       <c r="C53" t="s">
         <v>16</v>
       </c>
       <c r="E53" t="s">
-        <v>65</v>
-      </c>
-      <c r="F53" t="s">
+        <v>63</v>
+      </c>
+      <c r="F53" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="G53" t="s">
         <v>86</v>
       </c>
-      <c r="G53" t="s">
-        <v>89</v>
-      </c>
       <c r="H53" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="54" spans="1:8">
       <c r="H54" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="55" spans="1:8">
       <c r="H55" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="56" spans="1:8">
       <c r="H56" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="57" spans="1:8">
@@ -1046,97 +1188,97 @@
     <row r="59" spans="1:8">
       <c r="H59" s="1"/>
     </row>
-    <row r="60" spans="1:8">
+    <row r="60" spans="1:8" ht="27">
       <c r="C60" t="s">
-        <v>17</v>
+        <v>96</v>
       </c>
       <c r="E60" t="s">
-        <v>64</v>
-      </c>
-      <c r="F60" t="s">
-        <v>87</v>
+        <v>62</v>
+      </c>
+      <c r="F60" s="5" t="s">
+        <v>84</v>
       </c>
       <c r="H60" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="61" spans="1:8">
       <c r="H61" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="69" spans="1:8">
       <c r="A69" t="s">
+        <v>22</v>
+      </c>
+      <c r="C69" t="s">
+        <v>22</v>
+      </c>
+      <c r="E69" t="s">
+        <v>61</v>
+      </c>
+      <c r="F69" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="C69" t="s">
-        <v>23</v>
-      </c>
-      <c r="E69" t="s">
-        <v>63</v>
-      </c>
-      <c r="F69" t="s">
+      <c r="G69" t="s">
         <v>24</v>
       </c>
-      <c r="G69" t="s">
+      <c r="H69" t="s">
         <v>25</v>
-      </c>
-      <c r="H69" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="70" spans="1:8">
       <c r="H70" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="71" spans="1:8">
       <c r="H71" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="74" spans="1:8">
       <c r="C74" t="s">
+        <v>26</v>
+      </c>
+      <c r="E74" t="s">
+        <v>64</v>
+      </c>
+      <c r="F74" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="E74" t="s">
-        <v>66</v>
-      </c>
-      <c r="F74" t="s">
+      <c r="G74" t="s">
+        <v>29</v>
+      </c>
+      <c r="H74" t="s">
         <v>28</v>
-      </c>
-      <c r="G74" t="s">
-        <v>30</v>
-      </c>
-      <c r="H74" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="75" spans="1:8">
       <c r="H75" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="76" spans="1:8">
       <c r="H76" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="78" spans="1:8">
       <c r="C78" t="s">
+        <v>97</v>
+      </c>
+      <c r="E78" t="s">
+        <v>75</v>
+      </c>
+      <c r="F78" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="E78" t="s">
-        <v>77</v>
-      </c>
-      <c r="F78" t="s">
-        <v>35</v>
-      </c>
       <c r="G78" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H78" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>
@@ -1178,17 +1320,17 @@
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -1207,12 +1349,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>
@@ -1231,4 +1373,92 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E9"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
+  <cols>
+    <col min="1" max="1" width="13.375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.75" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="36.5" customWidth="1"/>
+    <col min="4" max="4" width="54.125" style="5" customWidth="1"/>
+    <col min="5" max="5" width="37.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C1" t="s">
+        <v>102</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="40.5">
+      <c r="A2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="C3" s="5"/>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="C4" s="5"/>
+      <c r="E4" s="1"/>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="C5" s="5"/>
+    </row>
+    <row r="6" spans="1:5" ht="27">
+      <c r="A6" t="s">
+        <v>98</v>
+      </c>
+      <c r="B6" t="s">
+        <v>90</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="E6" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="C7" s="5"/>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="C8" s="5"/>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="B9" t="s">
+        <v>92</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="E9" t="s">
+        <v>94</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/internal_doc/03.开发设计/OM_Agent接口.xlsx
+++ b/internal_doc/03.开发设计/OM_Agent接口.xlsx
@@ -12,14 +12,14 @@
     <sheet name="底层提供" sheetId="4" r:id="rId3"/>
     <sheet name="问题" sheetId="5" r:id="rId4"/>
     <sheet name="Sheet2" sheetId="6" r:id="rId5"/>
-    <sheet name="Sheet1" sheetId="7" r:id="rId6"/>
+    <sheet name="om_agent接口" sheetId="7" r:id="rId6"/>
   </sheets>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="116">
   <si>
     <t>检测host</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -437,7 +437,51 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>{"rc":SDB_OK,HostInfo:{[{ip:134,hostname:"ubuntu-dev1",canPing:true/false, canSsh:true/false, rc:SDB_OK},...]}</t>
+    <t>{"rc":SDB_OK,HostInfo:{[{IP:"",HostName:"ubuntu-dev1",Ping:true/false, Ssh:true/false, rc:SDB_OK},...]}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>发给本地Agent，由本地Agent做检测</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>发给本地Agent，由本地Agent做扫描</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>按照OM架构设计.docx中host表结构</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>添加host</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>add host</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{SdbUser, SdbPasswd, SdbUserGroup, HostInfo:[{IP,HostName,User, Passwd, SshPort, AgentPort, InstallPath}]}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>全部安装成功才返回成功，否则返回失败并由agent将环境清理干净</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{rc, TransactionID}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>add business</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>添加业务（安装）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"BusinessType":"sequoiadb","BusinessName":"b1", "DeployMod":"xx", "ClusterName":"c1", "Config":[{"HostName": "host1", "User":"root", "Passwd":"root", "datagroupname": "", "dbpath": "/home/db2/standalone/11830", "svcname": "11830", ...}]}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1377,14 +1421,14 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="13.375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.75" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="36.5" customWidth="1"/>
+    <col min="1" max="1" width="17.25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="46.375" style="5" customWidth="1"/>
     <col min="4" max="4" width="54.125" style="5" customWidth="1"/>
-    <col min="5" max="5" width="37.5" customWidth="1"/>
+    <col min="5" max="5" width="37.5" style="5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -1394,7 +1438,7 @@
       <c r="B1" t="s">
         <v>100</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="5" t="s">
         <v>102</v>
       </c>
       <c r="D1" s="5" t="s">
@@ -1414,46 +1458,67 @@
       <c r="D2" s="5" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="C3" s="5"/>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="C4" s="5"/>
-      <c r="E4" s="1"/>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="C5" s="5"/>
-    </row>
-    <row r="6" spans="1:5" ht="27">
-      <c r="A6" t="s">
+      <c r="E2" s="5" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="40.5">
+      <c r="A4" t="s">
         <v>98</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B4" t="s">
         <v>90</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C4" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="E6" t="s">
-        <v>95</v>
+      <c r="D4" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="7" spans="1:5">
-      <c r="C7" s="5"/>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="C8" s="5"/>
-    </row>
-    <row r="9" spans="1:5">
+      <c r="B7" t="s">
+        <v>92</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="40.5">
+      <c r="A9" t="s">
+        <v>108</v>
+      </c>
       <c r="B9" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="E9" t="s">
-        <v>94</v>
+        <v>110</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="94.5">
+      <c r="A11" t="s">
+        <v>114</v>
+      </c>
+      <c r="B11" t="s">
+        <v>113</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>115</v>
       </c>
     </row>
   </sheetData>

--- a/internal_doc/03.开发设计/OM_Agent接口.xlsx
+++ b/internal_doc/03.开发设计/OM_Agent接口.xlsx
@@ -11,7 +11,7 @@
     <sheet name="内部接口" sheetId="3" r:id="rId2"/>
     <sheet name="底层提供" sheetId="4" r:id="rId3"/>
     <sheet name="问题" sheetId="5" r:id="rId4"/>
-    <sheet name="Sheet2" sheetId="6" r:id="rId5"/>
+    <sheet name="问题2" sheetId="6" r:id="rId5"/>
     <sheet name="om_agent接口" sheetId="7" r:id="rId6"/>
   </sheets>
   <calcPr calcId="124519"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="125">
   <si>
     <t>检测host</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -482,6 +482,42 @@
   </si>
   <si>
     <t>{"BusinessType":"sequoiadb","BusinessName":"b1", "DeployMod":"xx", "ClusterName":"c1", "Config":[{"HostName": "host1", "User":"root", "Passwd":"root", "datagroupname": "", "dbpath": "/home/db2/standalone/11830", "svcname": "11830", ...}]}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>扫描机器非业务型失败后，该返回NULL还是FALSE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>install remote agent</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{HostInfo:[{IP/HostName,User, Passwd, SshPort, AgentPort},...]}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"rc":SDB_OK,"Detail":""}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>exit agent</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>uninstall remote agent{}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>发给远程 Agent</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>发给本地Agent</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -568,74 +604,6 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -647,7 +615,7 @@
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="C7EDCC"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -1023,7 +991,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="54">
+    <row r="21" spans="1:8" ht="40.5">
       <c r="C21" t="s">
         <v>3</v>
       </c>
@@ -1055,7 +1023,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="27">
+    <row r="26" spans="1:8">
       <c r="C26" t="s">
         <v>49</v>
       </c>
@@ -1191,7 +1159,7 @@
     <row r="52" spans="1:8">
       <c r="H52" s="1"/>
     </row>
-    <row r="53" spans="1:8" ht="27">
+    <row r="53" spans="1:8">
       <c r="C53" t="s">
         <v>16</v>
       </c>
@@ -1232,7 +1200,7 @@
     <row r="59" spans="1:8">
       <c r="H59" s="1"/>
     </row>
-    <row r="60" spans="1:8" ht="27">
+    <row r="60" spans="1:8">
       <c r="C60" t="s">
         <v>96</v>
       </c>
@@ -1412,7 +1380,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+  </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -1421,7 +1395,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="17.25" bestFit="1" customWidth="1"/>
@@ -1479,45 +1453,84 @@
         <v>105</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
-      <c r="B7" t="s">
+    <row r="6" spans="1:5" ht="27">
+      <c r="B6" t="s">
+        <v>117</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="B8" t="s">
         <v>92</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C8" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D8" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="E8" s="5" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="40.5">
-      <c r="A9" t="s">
+    <row r="10" spans="1:5">
+      <c r="B10" t="s">
+        <v>121</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="27">
+      <c r="B12" t="s">
+        <v>122</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="40.5">
+      <c r="A15" t="s">
         <v>108</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B15" t="s">
         <v>109</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C15" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D15" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="E15" s="5" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="94.5">
-      <c r="A11" t="s">
+    <row r="17" spans="1:3" ht="94.5">
+      <c r="A17" t="s">
         <v>114</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B17" t="s">
         <v>113</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C17" s="5" t="s">
         <v>115</v>
       </c>
     </row>

--- a/internal_doc/03.开发设计/OM_Agent接口.xlsx
+++ b/internal_doc/03.开发设计/OM_Agent接口.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="127">
   <si>
     <t>检测host</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -518,6 +518,14 @@
   </si>
   <si>
     <t>发给本地Agent</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{HostInfo:[{IP,HostName,User, Passwd, SshPort, AgentPort},...]}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"Rc":SDB_OK,"Detail":"", HostInfo:[{"Rc":0,"IP":"", "IsNeedUninstall":true}]}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1399,7 +1407,7 @@
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="17.25" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.125" customWidth="1"/>
     <col min="3" max="3" width="46.375" style="5" customWidth="1"/>
     <col min="4" max="4" width="54.125" style="5" customWidth="1"/>
     <col min="5" max="5" width="37.5" style="5" customWidth="1"/>
@@ -1444,7 +1452,7 @@
         <v>90</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>91</v>
+        <v>125</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>104</v>
@@ -1458,10 +1466,10 @@
         <v>117</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="E6" s="5" t="s">
         <v>124</v>

--- a/internal_doc/03.开发设计/OM_Agent接口.xlsx
+++ b/internal_doc/03.开发设计/OM_Agent接口.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14385" windowHeight="7485" activeTab="5"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14385" windowHeight="7485" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="与OMSvc接口" sheetId="2" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="139">
   <si>
     <t>检测host</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -485,10 +485,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>扫描机器非业务型失败后，该返回NULL还是FALSE</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>install remote agent</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -505,14 +501,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>exit agent</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>uninstall remote agent{}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>发给远程 Agent</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -526,6 +514,66 @@
   </si>
   <si>
     <t>{"Rc":SDB_OK,"Detail":"", HostInfo:[{"Rc":0,"IP":"", "IsNeedUninstall":true}]}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>shut down</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>uninstall remote agent</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>无法删除catalog</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>问题</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>描述</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在安装失败后，需要清理环境，其中已安装的catalog无法删除</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在安装虚拟coord的时候，需要使用本地的一个有效随机端口</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>无法获取本地某个端口的使用状态</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>无法检测远端机器是否运行某个进程</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>目前处理方式</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>暂时使用13579本地端口</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在checkhost时，需要在远端安装一个临时的cm,但是不知道远端是否已经安装有cm</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不管远端是否已安装cm,一律先把它停一次，然后再安装新的临时cm</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>虚coord暂时无法创建coord</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>checkhost返回信息暂时不齐全，详情查看checkhost信息.docx</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1386,13 +1434,65 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
+  <cols>
+    <col min="1" max="1" width="41.5" customWidth="1"/>
+    <col min="2" max="2" width="49.625" customWidth="1"/>
+    <col min="3" max="3" width="44.5" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>116</v>
-      </c>
+        <v>127</v>
+      </c>
+      <c r="B1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="27">
+      <c r="A2" t="s">
+        <v>126</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="27">
+      <c r="A3" t="s">
+        <v>131</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="C3" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="27">
+      <c r="A4" t="s">
+        <v>132</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="27">
+      <c r="A6" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="C6" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -1452,7 +1552,7 @@
         <v>90</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>104</v>
@@ -1463,16 +1563,16 @@
     </row>
     <row r="6" spans="1:5" ht="27">
       <c r="B6" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -1491,27 +1591,27 @@
     </row>
     <row r="10" spans="1:5">
       <c r="B10" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="27">
       <c r="B12" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="C12" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="D12" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="D12" s="5" t="s">
-        <v>120</v>
-      </c>
       <c r="E12" s="5" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="40.5">

--- a/internal_doc/03.开发设计/OM_Agent接口.xlsx
+++ b/internal_doc/03.开发设计/OM_Agent接口.xlsx
@@ -4,43 +4,29 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14385" windowHeight="7485" activeTab="4"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14385" windowHeight="7485"/>
   </bookViews>
   <sheets>
-    <sheet name="与OMSvc接口" sheetId="2" r:id="rId1"/>
-    <sheet name="内部接口" sheetId="3" r:id="rId2"/>
-    <sheet name="底层提供" sheetId="4" r:id="rId3"/>
-    <sheet name="问题" sheetId="5" r:id="rId4"/>
-    <sheet name="问题2" sheetId="6" r:id="rId5"/>
-    <sheet name="om_agent接口" sheetId="7" r:id="rId6"/>
+    <sheet name="omagent需求（初稿）" sheetId="2" r:id="rId1"/>
+    <sheet name="omagent遗留问题" sheetId="6" r:id="rId2"/>
+    <sheet name="om_svc_agent接口" sheetId="8" r:id="rId3"/>
+    <sheet name="agent_js接口" sheetId="9" r:id="rId4"/>
   </sheets>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="220">
   <si>
     <t>检测host</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>ping</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ssh</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>安装remote_agent</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>scp</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>参数</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -285,10 +271,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>启动进程命令</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>3、检测CPU（型号，核数，主频）</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -313,14 +295,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>检测端口状态</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>操作系统信息获取（见gethostinfo）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>testSvc</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -373,14 +347,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>ssh没开启，返回结果不够准确。reval is: { "": { "Ping": true, "Ssh": false, "HostName": null, "Rc": -10, "Detail": "{ \"ErrMsg\": \"Authentication failed (username/password)\" }" } }</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>部分机器ssh功能已开启，但通过new Ssh()连不上</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>basic check</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -425,10 +391,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>扫描host</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>参数</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -437,10 +399,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>{"rc":SDB_OK,HostInfo:{[{IP:"",HostName:"ubuntu-dev1",Ping:true/false, Ssh:true/false, rc:SDB_OK},...]}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>发给本地Agent，由本地Agent做检测</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -457,14 +415,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>add host</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{SdbUser, SdbPasswd, SdbUserGroup, HostInfo:[{IP,HostName,User, Passwd, SshPort, AgentPort, InstallPath}]}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>全部安装成功才返回成功，否则返回失败并由agent将环境清理干净</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -473,7 +423,911 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>add business</t>
+    <t>无法删除catalog</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>问题</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>描述</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>目前处理方式</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>checkhost返回信息暂时不齐全，详情查看checkhost信息.docx</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>getLastErrMsg会返回undefined</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>scanHost.js</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>$scan host</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>扫描机器</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>获取机器信息</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>$basic check</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>basicCheckHost.js</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>$install remote agent</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>installRemoteAgent.js</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>$uninstall remote agent</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>uninstallRemoteAgent.js</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>添加机器</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>$add host</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>addHost.js</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>$check host</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>checkHost.js,checkHostItem.js</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>$shutdown</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NULL</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>$query progress</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>添加业务</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>$add business</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>createTempCoord.js，createCatalog.js， createCoord.js，createDataNode.js，createStandalone.js，removeStandalone.js，removeDataRG.js，removeCoordRG.js，removeCatalogRG.js，removeTempCoord.js，rollbackCatalog.js，rollbackCoord.js，rollbackDataNode.js</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+    "SdbUser": "sdbadmin", 
+    "SdbPasswd": "sdb     admin", 
+    "SdbUserGroup": "sdbadmin_group", 
+    "Config": [
+        {
+            "HostName": "rhel64-test8", 
+            "datagro     upname": "", 
+            "dbpath": "/sequoiadb/database/coord/11810", 
+            "svcname": "11810", 
+            "role": "coord     ", 
+            "diaglevel": "3", 
+            "hjbuf": "128", 
+            "logbuffsize": "1024", 
+            "logfilenum": "20", 
+            "logfilesz": "64", 
+            "maxprefpool": "200", 
+            "maxreplsync": "10", 
+            "numpagecleaners": "1", 
+            "numpreload": "0", 
+            "pagecleaninterval": "1000", 
+            "preferedinstance": "A", 
+            "sortbuf": "512", 
+            "syncstrategy": "no     ne", 
+            "transactionon": "false", 
+            "User": "root", 
+            "Passwd": "sequoiadb", 
+            "SshPort": "22"
+        }, 
+        {
+            "     HostName": "rhel64-test8", 
+            "datagroupname": "", 
+            "dbpath": "/sequoiadb/database/catalog/11820     ", 
+            "svcname": "11820", 
+            "role": "catalog", 
+            "diaglevel": "3", 
+            "hjbuf": "128", 
+            "logbuffsize": "     1024", 
+            "logfilenum": "20", 
+            "logfilesz": "64", 
+            "maxprefpool": "200", 
+            "maxreplsync": "10", 
+            "nu     mpagecleaners": "1", 
+            "numpreload": "0", 
+            "pagecleaninterval": "1000", 
+            "preferedinstance": "A", 
+            "sortbuf": "512", 
+            "syncstrategy": "none", 
+            "transactionon": "false", 
+            "User": "root", 
+            "Passw     d": "sequoiadb", 
+            "SshPort": "22"
+        }, 
+        {
+            "HostName": "rhel64-test8", 
+            "datagroupname": "group1", 
+            "dbpath": "/sequoiadb/database/data/11830", 
+            "svcname": "11830", 
+            "role": "data", 
+            "diaglevel": "3", 
+            "hjbuf": "128", 
+            "logbuffsize": "1024", 
+            "logfilenum": "20", 
+            "logfilesz": "64", 
+            "maxpre     fpool": "200", 
+            "maxreplsync": "10", 
+            "numpagecleaners": "1", 
+            "numpreload": "0", 
+            "pagecleanint     erval": "1000", 
+            "preferedinstance": "A", 
+            "sortbuf": "512", 
+            "syncstrategy": "none", 
+            "transact     ionon": "false", 
+            "User": "root", 
+            "Passwd": "sequoiadb", 
+            "SshPort": "22"
+        }
+    ], 
+    "ClusterName": "myCluster", 
+    "BusinessName": "myBusiness", 
+    "BusinessType": "sequoiadb", 
+    "DeployMod": "distri     bution", 
+    "TaskID": 3
+}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>更新host表</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>$update hostname</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+    "HostName": "susetzb", 
+    "IP": "127.0.0.1", 
+    "User": "", 
+    "Passwd": "", 
+    "HostInfo": [
+        {
+            "HostName": "rhel64-test8", 
+            "IP": "192.168.20.165"
+        }
+    ]
+}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>发给集群的每一台机器</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>updateHostsInfo.js</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>createTempCoord.js</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> var BUS_JSON = { "CataAddr": [] };</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>createCatalog.js</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>var BUS_JSON = {
+    "InstallHostName": "rhel64-test8", 
+    "InstallSvcName": "11820", 
+    "InstallPath": "/sequoiadb/database/catalog/11820", 
+    "InstallConfig": {
+        "role": "catalog", 
+        "diaglevel": "3", 
+        "hjbuf": "128", 
+        "logbuffsize": "1024", 
+        "logfilenum": "20", 
+        "logfilesz": "64", 
+        "maxprefpool": "200", 
+        "maxreplsync": "10", 
+        "numpagecleaners": "1", 
+        "numpreload": "0", 
+        "pagecleaninterval": "1000", 
+        "preferedinstance": "A", 
+        "sortbuf": "512", 
+        "syncstrategy": "none", 
+        "transactionon": "false"
+    }
+}; var SYS_JSON = {
+    "VCoordSvcName": "10000", 
+    "SdbUser": "sdbadmin", 
+    "SdbPasswd": "sdbadmin", 
+    "SdbUserGroup": "sdbadmin_group", 
+    "User": "root", 
+    "Passwd": "sequoiadb", 
+    "SshPort": "22"
+};</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>createCoord.js</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>var BUS_JSON = {
+    "InstallHostName": "rhel64-test8", 
+    "InstallSvcName": "11810", 
+    "InstallPath": "/sequoiadb/database/coord/11810", 
+    "InstallConfig": {
+        "role": "coord", 
+        "diaglevel": "3", 
+        "hjbuf": "128", 
+        "logbuffsize": "1024", 
+        "logfilenum": "20", 
+        "logfilesz": "64", 
+        "maxprefpool": "200", 
+        "maxreplsync": "10", 
+        "numpagecleaners": "1", 
+        "numpreload": "0", 
+        "pagecleaninterval": "1000", 
+        "preferedinstance": "A", 
+        "sortbuf": "512", 
+        "syncstrategy": "none", 
+        "transactionon": "false"
+    }
+}; var SYS_JSON = {
+    "VCoordSvcName": "10000", 
+    "SdbUser": "sdbadmin", 
+    "SdbPasswd": "sdbadmin", 
+    "SdbUserGroup": "sdbadmin_group", 
+    "User": "root", 
+    "Passwd": "sequoiadb", 
+    "SshPort": "22"
+};</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>createDataNode.js</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>var BUS_JSON = {
+    "InstallGroupName": "group1", 
+    "InstallHostName": "rhel64-test8", 
+    "InstallSvcName": "11830", 
+    "InstallPath": "/sequoiadb/database/data/11830", 
+    "InstallConfig": {
+        "role": "data", 
+        "diaglevel": "3", 
+        "hjbuf": "128", 
+        "logbuffsize": "1024", 
+        "logfilenum": "20", 
+        "logfilesz": "64", 
+        "maxprefpool": "200", 
+        "maxreplsync": "10", 
+        "numpagecleaners": "1", 
+        "numpreload": "0", 
+        "pagecleaninterval": "1000", 
+        "preferedinstance": "A", 
+        "sortbuf": "512", 
+        "syncstrategy": "none", 
+        "transactionon": "false"
+    }
+};var SYS_JSON = {
+    "VCoordSvcName": "10000", 
+    "SdbUser": "sdbadmin", 
+    "SdbPasswd": "sdbadmin", 
+    "SdbUserGroup": "sdbadmin_group", 
+    "User": "root", 
+    "Passwd": "sequoiadb", 
+    "SshPort": "22"
+}
+;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>删除业务</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>$remove business</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>createTempCoord.js，removeStandalone.js，removeDataRG.js，removeCoordRG.js，removeCatalogRG.js，removeTempCoord.js，</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+    "TaskID": 4, 
+    "Config": [
+        {
+            "datagroupname": "", 
+            "dbpath": "/sequoiadb/database/coord/11810", 
+            "svcname": "11810", 
+            "role": "coord", 
+            "diaglevel": "3", 
+            "hjbuf": "128", 
+            "logbuffsize": "1024", 
+            "logfilenum": "20", 
+            "logfilesz": "64", 
+            "maxprefpool": "200", 
+            "maxreplsync": "10", 
+            "numpagecleaners": "1", 
+            "numpreload": "0", 
+            "pagecleaninterval": "1000", 
+            "preferedinstance": "A", 
+            "sortbuf": "512", 
+            "syncstrategy": "none", 
+            "transactionon": "false", 
+            "SshPort": "22", 
+            "catalogname": "11813", 
+            "HostName": "rhel64-test8", 
+            "User": "root", 
+            "Passwd": "sequoiadb"
+        }, 
+        {
+            "datagroupname": "", 
+            "dbpath": "/sequoiadb/database/catalog/11820", 
+            "svcname": "11820", 
+            "role": "catalog", 
+            "diaglevel": "3", 
+            "hjbuf": "128", 
+            "logbuffsize": "1024", 
+            "logfilenum": "20", 
+            "logfilesz": "64", 
+            "maxprefpool": "200", 
+            "maxreplsync": "10", 
+            "numpagecleaners": "1", 
+            "numpreload": "0", 
+            "pagecleaninterval": "1000", 
+            "preferedinstance": "A", 
+            "sortbuf": "512", 
+            "syncstrategy": "none", 
+            "transactionon": "false", 
+            "SshPort": "22", 
+            "catalogname": "11823", 
+            "HostName": "rhel64-test8", 
+            "User": "root", 
+            "Passwd": "sequoiadb"
+        }, 
+        {
+            "datagroupname": "group1", 
+            "dbpath": "/sequoiadb/database/data/11830", 
+            "svcname": "11830", 
+            "role": "data", 
+            "diaglevel": "3", 
+            "hjbuf": "128", 
+            "logbuffsize": "1024", 
+            "logfilenum": "20", 
+            "logfilesz": "64", 
+            "maxprefpool": "200", 
+            "maxreplsync": "10", 
+            "numpagecleaners": "1", 
+            "numpreload": "0", 
+            "pagecleaninterval": "1000", 
+            "preferedinstance": "A", 
+            "sortbuf": "512", 
+            "syncstrategy": "none", 
+            "transactionon": "false", 
+            "SshPort": "22", 
+            "catalogname": "11833", 
+            "HostName": "rhel64-test8", 
+            "User": "root", 
+            "Passwd": "sequoiadb"
+        }
+    ], 
+    "AuthUser": "", 
+    "AuthPasswd": "", 
+    "ClusterName": "myCluster", 
+    "BusinessType": "sequoiadb", 
+    "BusinessName": "myBusiness", 
+    "DeployMod": "distribution"
+}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>查询业务（安装)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>查询业务（删除)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{ "TaskID": 4 }</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{ "TaskID": XX }</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">{
+    "TaskID": 3, 
+    "IsFinish": false, 
+    "Status": "install", 
+    "ErrMsg": "", 
+    "Progress": [
+        {
+            "Name": "Catalog", 
+            "TotalCount": 1, 
+            "InstalledCount": 0, 
+            "Desc": "Installing catalog[rhel64-test8:11820]"
+        }, 
+        {
+            "Name": "Coord", 
+            "TotalCount": 1, 
+            "InstalledCount": 0, 
+            "Desc": ""
+        }, 
+        {
+            "Name": "group1", 
+            "TotalCount": 1, 
+            "InstalledCount": 0, 
+            "Desc": ""
+        }
+    ]
+}
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{ "TaskID": 3 }</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>removeTempCoord.js</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>var SYS_JSON = { "VCoordSvcName": "10000" };</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>查询业务（添加主机，添加业务，删除业务）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>removeStandalone.js</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>removeDataRG.js</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>removeCoordRG.js</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>removeCatalogRG.js</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> var BUS_JSON = {
+    "HostName": "susetzb", 
+    "IP": "127.0.0.1", 
+    "User": "", 
+    "Passwd": "", 
+    "HostInfo": [
+        {
+            "HostName": "rhel64-test8", 
+            "IP": "192.168.20.165"
+        }
+    ]
+};</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>var BUS_JSON = {
+    "SdbUser": "sdbadmin", 
+    "SdbPasswd": "sdbadmin", 
+    "SdbUserGroup": "sdbadmin_group", 
+    "InstallPacket": "/opt/sequoiadb/bin/../packet/sequoiadb-1.10-linux_x86_64-installer.run", 
+    "HostInfo": [
+        {
+            "IP": "192.168.20.165", 
+            "HostName": "rhel64-test8", 
+            "User": "root", 
+            "Passwd": "sequoiadb", 
+            "SshPort": "22", 
+            "AgentPort": "11790", 
+            "InstallPath": "/opt/sequoiadb/"
+        }
+    ]
+};</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>$remove host</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>删除机器</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>removeHost.js</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+    "HostName": "rhel64-test8", 
+    "IP": "192.168.20.165", 
+    "User": "root", 
+    "Passwd": "sequoiadb", 
+    "InstallPath": "/opt/sequoiadb/", 
+    "SshPort": "22"
+}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>var BUS_JSON = {
+    "HostName": "rhel64-test8", 
+    "IP": "192.168.20.165", 
+    "User": "root", 
+    "Passwd": "sequoiadb", 
+    "InstallPath": "/opt/sequoiadb/", 
+    "SshPort": "22"
+}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+    "HostInfo": [
+        {
+            "IP": "192.168.20.165", 
+            "User": "root", 
+            "Passwd": "sequoiadb", 
+            "SshPort": "22"
+        }
+    ]
+}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+    "HostInfo": [
+        {
+            "errno": 0, 
+            "detail": "", 
+            "Ping": true, 
+            "Ssh": true, 
+            "HostName": "rhel64-test8", 
+            "IP": "192.168.20.165"
+        }
+    ]
+}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{HostInfo:[{IP/HostName,User, Passwd, SshPort},...]}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{HostInfo:[{errno,detail,Ping,Ssh,HostName,IP},...]}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{HostInfo:[{IP,HostName,User, Passwd, SshPort},...]}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{HostInfo:[{errno,detail,IsNeedUninstall,AgentPort,IP},...]}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>发给本地Agent</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+    "IP": "192.168.20.165", 
+    "HostName": "rhel64-test8", 
+    "OS": {
+        "Distributor": "RedHatEnterpriseServer", 
+        "Release": "6.4", 
+        "Bit": 64
+    }, 
+    "OM": {
+        "HasInstalled": false, 
+        "Version": "", 
+        "Path": "", 
+        "Port": "", 
+        "Release": ""
+    }, 
+    "CPU": [
+        {
+            "ID": "", 
+            "Model": "Intel(R) Xeon(R) CPU E5-2620 0 ", 
+            "Core": 2, 
+            "Freq": "2.00GHz"
+        }
+    ], 
+    "Memory": {
+        "Model": "", 
+        "Size": 2887, 
+        "Free": 2310
+    }, 
+    "Disk": [
+        {
+            "Name": "/dev/mapper/vg_rhel64test8-lv_root", 
+            "Mount": "/", 
+            "Size": 43659, 
+            "Free": 39539, 
+            "IsLocal": true
+        }, 
+        {
+            "Name": "/dev/sda1", 
+            "Mount": "/boot", 
+            "Size": 460, 
+            "Free": 423, 
+            "IsLocal": true
+        }, 
+        {
+            "Name": "//192.168.20.10/files", 
+            "Mount": "/mnt", 
+            "Size": 47837, 
+            "Free": 5970, 
+            "IsLocal": false
+        }
+    ], 
+    "Net": [
+        {
+            "Name": "lo", 
+            "Model": "", 
+            "Bandwidth": "", 
+            "IP": "127.0.0.1"
+        }, 
+        {
+            "Name": "eth0", 
+            "Model": "", 
+            "Bandwidth": "", 
+            "IP": "192.168.20.165"
+        }
+    ], 
+    "Port": [
+        {
+            "Port": "", 
+            "CanUse": false
+        }
+    ], 
+    "Service": [
+        {
+            "Name": "", 
+            "IsRunning": false, 
+            "Version": ""
+        }
+    ], 
+    "Safety": {
+        "Name": "", 
+        "Context": "", 
+        "IsRunning": false
+    }
+}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{IP，HostName，User, Passwd}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+    "HostInfo": [
+        {
+            "errno": 0, 
+            "detail": "", 
+            "IsNeedUninstall": true, 
+            "AgentPort": "10000", 
+            "IP": "192.168.20.165"
+        }
+    ]
+}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">{
+    "HostInfo": [
+        {
+            "IP": "192.168.20.165", 
+            "HostName": "rhel64-test8", 
+            "User": "root", 
+            "Passwd": "sequoiadb", 
+            "SshPort": "22"
+        }
+    ]
+}
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+    "HostInfo": [
+        {
+            "errno": 0, 
+            "detail": "", 
+            "Ping": true, 
+            "Ssh": true, 
+            "IP": "192.168.20.165"
+        }
+    ]
+}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>$shut down</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{HostInfo:[{errno,detail,IP},...]}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+    "HostInfo": [
+        {
+            "errno": 0, 
+            "detail": "", 
+            "IP": "192.168.20.165"
+        }
+    ]
+}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>发给远程Agent</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{SdbUser, SdbPasswd, SdbUserGroup, InstallPacket，HostInfo:[{IP,HostName,User, Passwd, SshPort, AgentPort, InstallPath}]}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{ "TransactionID": 0 } // no need</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{HostName,IP,User,Passwd,HostInfo:[HostName,IP]}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+    "SdbUser": "sdbadmin", 
+    "SdbPasswd": "sdbadmin", 
+    "SdbUserGroup": "sdbadmin_group", 
+    "Config": [
+        {
+            "HostName": "rhel64-test8", 
+            "datagroupname": "", 
+            "dbpath": "/sequoiadb/database/coord/11810", 
+            "svcname": "11810", 
+            "role": "coord     ", 
+            "diaglevel": "3", 
+            "hjbuf": "128", 
+            "logbuffsize": "1024", 
+            "logfilenum": "20", 
+            "logfilesz": "64", 
+            "maxprefpool": "200", 
+            "maxreplsync": "10", 
+            "numpagecleaners": "1", 
+            "numpreload": "0", 
+            "pagecleaninterval": "1000", 
+            "preferedinstance": "A", 
+            "sortbuf": "512", 
+            "syncstrategy": "none", 
+            "transactionon": "false", 
+            "User": "root", 
+            "Passwd": "sequoiadb", 
+            "SshPort": "22"
+        }, 
+        {
+            "HostName": "rhel64-test8", 
+            "datagroupname": "", 
+            "dbpath": "/sequoiadb/database/catalog/11820     ", 
+            "svcname": "11820", 
+            "role": "catalog", 
+            "diaglevel": "3", 
+            "hjbuf": "128", 
+            "logbuffsize": "1024", 
+            "logfilenum": "20", 
+            "logfilesz": "64", 
+            "maxprefpool": "200", 
+            "maxreplsync": "10", 
+            "numpagecleaners": "1", 
+            "numpreload": "0", 
+            "pagecleaninterval": "1000", 
+            "preferedinstance": "A", 
+            "sortbuf": "512", 
+            "syncstrategy": "none", 
+            "transactionon": "false", 
+            "User": "root", 
+            "Passwd": "sequoiadb", 
+            "SshPort": "22"
+        }, 
+        {
+            "HostName": "rhel64-test8", 
+            "datagroupname": "group1", 
+            "dbpath": "/sequoiadb/database/data/11830", 
+            "svcname": "11830", 
+            "role": "data", 
+            "diaglevel": "3", 
+            "hjbuf": "128", 
+            "logbuffsize": "1024", 
+            "logfilenum": "20", 
+            "logfilesz": "64", 
+            "maxprefpool": "200", 
+            "maxreplsync": "10", 
+            "numpagecleaners": "1", 
+            "numpreload": "0", 
+            "pagecleaninterval": "1000", 
+            "preferedinstance": "A", 
+            "sortbuf": "512", 
+            "syncstrategy": "none", 
+            "transactionon": "false", 
+            "User": "root", 
+            "Passwd": "sequoiadb", 
+            "SshPort": "22"
+        }
+    ], 
+    "ClusterName": "myCluster", 
+    "BusinessName": "myBusiness", 
+    "BusinessType": "sequoiadb", 
+    "DeployMod": "distribution", 
+    "TaskID": 3
+}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>结构复杂，如下用例所示</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -481,99 +1335,360 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>{"BusinessType":"sequoiadb","BusinessName":"b1", "DeployMod":"xx", "ClusterName":"c1", "Config":[{"HostName": "host1", "User":"root", "Passwd":"root", "datagroupname": "", "dbpath": "/home/db2/standalone/11830", "svcname": "11830", ...}]}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>install remote agent</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{HostInfo:[{IP/HostName,User, Passwd, SshPort, AgentPort},...]}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"rc":SDB_OK,"Detail":""}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>发给远程 Agent</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>发给本地Agent</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{HostInfo:[{IP,HostName,User, Passwd, SshPort, AgentPort},...]}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"Rc":SDB_OK,"Detail":"", HostInfo:[{"Rc":0,"IP":"", "IsNeedUninstall":true}]}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>shut down</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>uninstall remote agent</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>无法删除catalog</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>问题</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>描述</t>
+    <t>{TaskID,IsFinish,Status,ErrMsg,Progress:[{Name,TotalCount,InstalledCount, Desc},...]}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>结构复杂，如下所示</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+    "TaskID": 4, 
+    "IsFinish": false, 
+    "Status": "uninstall", 
+    "ErrMsg": "", 
+    "Progress": [
+        {
+            "Name": "Catalog", 
+            "TotalCount": 1, 
+            "UninstalledCount": 0, 
+            "Desc": "Removing catalog group"
+        }, 
+        {
+            "Name": "Coord", 
+            "TotalCount": 1, 
+            "UninstalledCount": 1, 
+            "Desc": "Finish removing coord group"
+        }, 
+        {
+            "Name": "group1", 
+            "TotalCount": 1, 
+            "UninstalledCount": 1, 
+            "Desc": "Finish removing data group[group1]"
+        }
+    ]
+}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>删除host</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>发给远端机器</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{HostName,IP,User,Passwd,InstallPath,SshPort}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">{
+    "HostInfo": [
+        {
+            "IP": "192.168.20.165", 
+            "HostName": "rhel64-test8", </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(no need)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+            "User": "root", 
+            "Passwd": "sequoiadb", 
+            "SshPort": "22"
+        }
+    ]
+}</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">{
+    "IP": "192.168.20.165", 
+    "HostName": "rhel64-test8", </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(no need)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+    "User": "root", 
+    "Passwd": "sequoiadb"
+}</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>{
+    "SdbUser": "sdbadmin", 
+    "SdbPasswd": "sdbadmin", 
+    "SdbUserGroup": "sdbadmin_group", 
+    "InstallPacket": "/opt/sequoiadb/bin/../packet/sequoiadb-1.10-linux_x86_64-installer.run", 
+    "HostInfo": [
+        {
+            "IP": "192.168.20.165", 
+            "HostName": "rhel64-test8",</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">(no need) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+            "User": "root", 
+            "Passwd": "sequoiadb", 
+            "SshPort": "22", 
+            "AgentPort": "11790", 
+            "InstallPath": "/opt/sequoiadb/"
+        }
+    ]
+}
+</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>删除业务（删除)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>修改记录</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2014.12.09 整理 by tzb</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>命令</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>命令字</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>js文件</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>参数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>返回值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+    "": {
+        "HostInfo": [
+            {
+                "errno": 0, 
+                "detail": "", 
+                "Ping": true, 
+                "Ssh": true, 
+                "HostName": "rhel64-test8", 
+                "IP": "192.168.20.165"
+            }
+        ]
+    }
+}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>var BUS_JSON = 
+{
+    "HostInfo": [
+        {
+            "IP": "192.168.20.165", 
+            "User": "root", 
+            "Passwd": "sequoiadb", 
+            "SshPort": "22"
+        }
+    ]
+};
+var SYS_JSON = {}; 
+var ENV_JSON = {}; 
+var OTHER_JSON = {};</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">{
+    "HostInfo": [
+        {
+            "errno": 0, 
+            "detail": "", 
+            "Ping": true, 
+            "Ssh": true, 
+            "IP": "192.168.20.165"
+        }
+    ]
+}
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>var BUS_JSON = 
+{
+    "HostInfo": [
+        {
+            "IP": "192.168.20.165", 
+            "HostName": "rhel64-test8", 
+            "User": "root", 
+            "Passwd": "sequoiadb", 
+            "SshPort": "22"
+        }
+    ]
+}; 
+var SYS_JSON = {}; 
+var ENV_JSON = {}; 
+var OTHER_JSON = {};</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>var BUS_JSON = 
+{
+    "IP": "192.168.20.165", 
+    "HostName": "rhel64-test8", 
+    "User": "root", 
+    "Passwd": "sequoiadb"
+};</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> var BUS_JSON = {
+    "HostInfo": [
+        {
+            "IP": "192.168.20.165", 
+            "HostName": "rhel64-test8", 
+            "User": "root", 
+            "Passwd": "sequoiadb", 
+            "SshPort": "22"
+        }
+    ]
+};</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>var BUS_JSON = 
+{
+    "HostInfo": [
+        {
+            "IP": "192.168.20.165", 
+            "HostName": "rhel64-test8", 
+            "User": "root", 
+            "Passwd": "sequoiadb", 
+            "SshPort": "22"
+        }
+    ]
+}; 
+var SYS_JSON = { "ProgPath": "/opt/sequoiadb/bin/" }; 
+var ENV_JSON = {}; 
+var OTHER_JSON = {};</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+    "errno": 0, 
+    "detail": "", 
+    "HostInfo": [
+        {
+            "errno": 0, 
+            "detail": "", 
+            "IP": "192.168.20.165", 
+            "HasInstall": true
+        }
+    ]
+}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>var BUS_JSON = {
+    "CataAddr": [
+        {
+            "HostName": "rhel64-test8", 
+            "CataSvcName": "11823"
+        }
+    ]
+};</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>var BUS_JSON = {
+    "AuthUser": "", 
+    "AuthPasswd": "", 
+    "UninstallGroupName": "group1"
+}; 
+var SYS_JSON = { "VCoordSvcName": "10000" };</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>var BUS_JSON = { "AuthUser": "", "AuthPasswd": "" }; 
+var SYS_JSON = { "VCoordSvcName": "10000" };</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> var BUS_JSON = { "AuthUser": "", "AuthPasswd": "" }; 
+var SYS_JSON = { "VCoordSvcName": "10000" };</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{ "VCoordSvcName": "10000" }</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>在安装失败后，需要清理环境，其中已安装的catalog无法删除</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>在安装虚拟coord的时候，需要使用本地的一个有效随机端口</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>无法获取本地某个端口的使用状态</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>无法检测远端机器是否运行某个进程</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>目前处理方式</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>暂时使用13579本地端口</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>在checkhost时，需要在远端安装一个临时的cm,但是不知道远端是否已经安装有cm</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>不管远端是否已安装cm,一律先把它停一次，然后再安装新的临时cm</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>虚coord暂时无法创建coord</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>checkhost返回信息暂时不齐全，详情查看checkhost信息.docx</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -581,7 +1696,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="6">
+  <fonts count="16">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -612,7 +1727,66 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0" tint="-0.14999847407452621"/>
+      <name val="宋体"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
@@ -620,20 +1794,54 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
-      <family val="2"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -641,22 +1849,159 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="3" xfId="3" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="3" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="3" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="3" xfId="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="3" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="3" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="4">
+    <cellStyle name="20% - Accent3" xfId="3" builtinId="38"/>
+    <cellStyle name="Accent3" xfId="2" builtinId="37"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Note" xfId="1" builtinId="10"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -954,86 +2299,86 @@
     <col min="1" max="1" width="14.5" customWidth="1"/>
     <col min="3" max="3" width="16.375" customWidth="1"/>
     <col min="5" max="5" width="19.375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="35.875" style="5" customWidth="1"/>
+    <col min="6" max="6" width="35.875" style="4" customWidth="1"/>
     <col min="7" max="7" width="34.625" customWidth="1"/>
     <col min="8" max="8" width="57.375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1" t="s">
         <v>34</v>
       </c>
-      <c r="C1" t="s">
-        <v>37</v>
-      </c>
       <c r="E1" t="s">
-        <v>59</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>5</v>
+        <v>56</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>2</v>
       </c>
       <c r="G1" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H1" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="27">
       <c r="A9" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C9" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E9" t="s">
-        <v>65</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>91</v>
+        <v>62</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>83</v>
       </c>
       <c r="G9" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="H9" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="H10" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="H11" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="27">
       <c r="E13" t="s">
-        <v>90</v>
-      </c>
-      <c r="F13" s="5" t="s">
-        <v>91</v>
+        <v>82</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>83</v>
       </c>
       <c r="H13" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="E16" t="s">
-        <v>92</v>
-      </c>
-      <c r="F16" s="5" t="s">
-        <v>93</v>
+        <v>84</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>85</v>
       </c>
       <c r="H16" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -1041,174 +2386,174 @@
         <v>0</v>
       </c>
       <c r="C19" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E19" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="40.5">
       <c r="C21" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E21" t="s">
-        <v>43</v>
-      </c>
-      <c r="F21" s="5" t="s">
-        <v>81</v>
+        <v>40</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>75</v>
       </c>
       <c r="G21" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="H21" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="22" spans="1:8">
       <c r="H22" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="23" spans="1:8">
       <c r="H23" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
     <row r="24" spans="1:8">
       <c r="H24" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="26" spans="1:8">
       <c r="C26" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E26" t="s">
-        <v>50</v>
-      </c>
-      <c r="F26" s="5" t="s">
-        <v>51</v>
+        <v>47</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>48</v>
       </c>
       <c r="G26" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H26" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
     </row>
     <row r="27" spans="1:8">
       <c r="H27" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="28" spans="1:8">
       <c r="H28" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
     </row>
     <row r="29" spans="1:8">
       <c r="H29" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
     </row>
     <row r="30" spans="1:8">
       <c r="H30" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
     </row>
     <row r="31" spans="1:8">
       <c r="H31" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
     </row>
     <row r="32" spans="1:8">
       <c r="H32" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="33" spans="3:8">
       <c r="H33" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34" spans="3:8">
       <c r="H34" s="2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="35" spans="3:8">
       <c r="H35" s="2" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="36" spans="3:8">
-      <c r="H36" s="4" t="s">
-        <v>78</v>
+      <c r="H36" s="3" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="37" spans="3:8">
-      <c r="H37" s="4" t="s">
-        <v>79</v>
+      <c r="H37" s="3" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="38" spans="3:8">
-      <c r="H38" s="4" t="s">
-        <v>77</v>
+      <c r="H38" s="3" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="41" spans="3:8">
       <c r="C41" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E41" t="s">
+        <v>49</v>
+      </c>
+      <c r="F41" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="G41" t="s">
+        <v>51</v>
+      </c>
+      <c r="H41" s="1" t="s">
         <v>52</v>
-      </c>
-      <c r="F41" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="G41" t="s">
-        <v>54</v>
-      </c>
-      <c r="H41" s="1" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="42" spans="3:8">
       <c r="H42" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="43" spans="3:8">
       <c r="H43" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="44" spans="3:8">
       <c r="H44" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="45" spans="3:8">
       <c r="H45" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="46" spans="3:8">
       <c r="H46" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="47" spans="3:8">
       <c r="H47" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="51" spans="1:8">
       <c r="A51" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C51" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="H51" s="1"/>
     </row>
@@ -1217,34 +2562,34 @@
     </row>
     <row r="53" spans="1:8">
       <c r="C53" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E53" t="s">
-        <v>63</v>
-      </c>
-      <c r="F53" s="5" t="s">
-        <v>83</v>
+        <v>60</v>
+      </c>
+      <c r="F53" s="4" t="s">
+        <v>77</v>
       </c>
       <c r="G53" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="H53" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="54" spans="1:8">
       <c r="H54" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="55" spans="1:8">
       <c r="H55" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="56" spans="1:8">
       <c r="H56" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="57" spans="1:8">
@@ -1258,95 +2603,95 @@
     </row>
     <row r="60" spans="1:8">
       <c r="C60" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="E60" t="s">
-        <v>62</v>
-      </c>
-      <c r="F60" s="5" t="s">
-        <v>84</v>
+        <v>59</v>
+      </c>
+      <c r="F60" s="4" t="s">
+        <v>78</v>
       </c>
       <c r="H60" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="61" spans="1:8">
       <c r="H61" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="69" spans="1:8">
       <c r="A69" t="s">
+        <v>19</v>
+      </c>
+      <c r="C69" t="s">
+        <v>19</v>
+      </c>
+      <c r="E69" t="s">
+        <v>58</v>
+      </c>
+      <c r="F69" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G69" t="s">
+        <v>21</v>
+      </c>
+      <c r="H69" t="s">
         <v>22</v>
-      </c>
-      <c r="C69" t="s">
-        <v>22</v>
-      </c>
-      <c r="E69" t="s">
-        <v>61</v>
-      </c>
-      <c r="F69" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="G69" t="s">
-        <v>24</v>
-      </c>
-      <c r="H69" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="70" spans="1:8">
       <c r="H70" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="71" spans="1:8">
       <c r="H71" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="74" spans="1:8">
       <c r="C74" t="s">
+        <v>23</v>
+      </c>
+      <c r="E74" t="s">
+        <v>61</v>
+      </c>
+      <c r="F74" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G74" t="s">
         <v>26</v>
       </c>
-      <c r="E74" t="s">
-        <v>64</v>
-      </c>
-      <c r="F74" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="G74" t="s">
-        <v>29</v>
-      </c>
       <c r="H74" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="75" spans="1:8">
       <c r="H75" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="76" spans="1:8">
       <c r="H76" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="78" spans="1:8">
       <c r="C78" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="E78" t="s">
-        <v>75</v>
-      </c>
-      <c r="F78" s="5" t="s">
-        <v>33</v>
+        <v>69</v>
+      </c>
+      <c r="F78" s="4" t="s">
+        <v>30</v>
       </c>
       <c r="G78" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="H78" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>
@@ -1358,83 +2703,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
-  <sheetData/>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A6"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1">
-      <c r="A2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1">
-      <c r="A4" s="3" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" t="s">
-        <v>74</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
-  <cols>
-    <col min="1" max="1" width="46.5" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1">
-      <c r="A2" t="s">
-        <v>89</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="41.5" customWidth="1"/>
@@ -1444,55 +2713,33 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>127</v>
+        <v>102</v>
       </c>
       <c r="B1" t="s">
-        <v>128</v>
+        <v>103</v>
       </c>
       <c r="C1" t="s">
-        <v>133</v>
+        <v>104</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="27">
       <c r="A2" t="s">
-        <v>126</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>129</v>
+        <v>101</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="27">
-      <c r="A3" t="s">
-        <v>131</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="C3" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="27">
+      <c r="A3" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="C3" s="4"/>
+    </row>
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>132</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="27">
-      <c r="A6" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="C6" s="5"/>
+        <v>106</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -1501,150 +2748,754 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E41"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="17.25" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.125" customWidth="1"/>
-    <col min="3" max="3" width="46.375" style="5" customWidth="1"/>
-    <col min="4" max="4" width="54.125" style="5" customWidth="1"/>
-    <col min="5" max="5" width="37.5" style="5" customWidth="1"/>
+    <col min="1" max="1" width="17.25" style="14" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.125" style="14" customWidth="1"/>
+    <col min="3" max="3" width="46.375" style="13" customWidth="1"/>
+    <col min="4" max="4" width="54.125" style="13" customWidth="1"/>
+    <col min="5" max="5" width="37.5" style="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" t="s">
+    <row r="1" spans="1:5" s="32" customFormat="1">
+      <c r="A1" s="30" t="s">
+        <v>199</v>
+      </c>
+      <c r="B1" s="30"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="14" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" s="7" customFormat="1">
+      <c r="A4" s="20" t="s">
+        <v>91</v>
+      </c>
+      <c r="B4" s="15" t="s">
+        <v>92</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="E4" s="10"/>
+    </row>
+    <row r="5" spans="1:5" s="5" customFormat="1" ht="27">
+      <c r="A5" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="E5" s="11" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" s="5" customFormat="1" ht="162">
+      <c r="A6" s="16"/>
+      <c r="B6" s="16"/>
+      <c r="C6" s="11" t="s">
+        <v>167</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>168</v>
+      </c>
+      <c r="E6" s="11"/>
+    </row>
+    <row r="8" spans="1:5" s="5" customFormat="1" ht="27">
+      <c r="A8" s="18" t="s">
+        <v>90</v>
+      </c>
+      <c r="B8" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>171</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" s="5" customFormat="1" ht="162">
+      <c r="A9" s="16"/>
+      <c r="B9" s="16"/>
+      <c r="C9" s="11" t="s">
+        <v>177</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>178</v>
+      </c>
+      <c r="E9" s="11"/>
+    </row>
+    <row r="11" spans="1:5" s="6" customFormat="1" ht="27">
+      <c r="A11" s="17"/>
+      <c r="B11" s="17" t="s">
+        <v>113</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>171</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>172</v>
+      </c>
+      <c r="E11" s="11" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" s="6" customFormat="1" ht="162">
+      <c r="A12" s="11"/>
+      <c r="B12" s="11"/>
+      <c r="C12" s="29" t="s">
+        <v>195</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="E12" s="11"/>
+    </row>
+    <row r="14" spans="1:5" s="5" customFormat="1">
+      <c r="A14" s="18"/>
+      <c r="B14" s="18" t="s">
+        <v>120</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>175</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="E14" s="11" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" s="5" customFormat="1" ht="409.5">
+      <c r="A15" s="16"/>
+      <c r="B15" s="16"/>
+      <c r="C15" s="29" t="s">
+        <v>196</v>
+      </c>
+      <c r="D15" s="11" t="s">
+        <v>174</v>
+      </c>
+      <c r="E15" s="11"/>
+    </row>
+    <row r="17" spans="1:5" s="9" customFormat="1">
+      <c r="A17" s="19"/>
+      <c r="B17" s="19" t="s">
+        <v>179</v>
+      </c>
+      <c r="C17" s="12" t="s">
+        <v>154</v>
+      </c>
+      <c r="D17" s="12"/>
+      <c r="E17" s="12" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" s="9" customFormat="1" ht="27">
+      <c r="A19" s="19"/>
+      <c r="B19" s="19" t="s">
+        <v>115</v>
+      </c>
+      <c r="C19" s="23" t="s">
+        <v>169</v>
+      </c>
+      <c r="D19" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="E19" s="12" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" s="9" customFormat="1" ht="162">
+      <c r="A20" s="21"/>
+      <c r="B20" s="21"/>
+      <c r="C20" s="23" t="s">
+        <v>195</v>
+      </c>
+      <c r="D20" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="E20" s="12"/>
+    </row>
+    <row r="22" spans="1:5" s="24" customFormat="1" ht="40.5">
+      <c r="A22" s="19" t="s">
+        <v>98</v>
+      </c>
+      <c r="B22" s="22" t="s">
+        <v>118</v>
+      </c>
+      <c r="C22" s="23" t="s">
+        <v>183</v>
+      </c>
+      <c r="D22" s="23" t="s">
+        <v>100</v>
+      </c>
+      <c r="E22" s="23" t="s">
         <v>99</v>
       </c>
-      <c r="B1" t="s">
-        <v>100</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="40.5">
-      <c r="A2" t="s">
-        <v>101</v>
-      </c>
-      <c r="B2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="40.5">
-      <c r="A4" t="s">
-        <v>98</v>
-      </c>
-      <c r="B4" t="s">
-        <v>90</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="27">
-      <c r="B6" t="s">
-        <v>116</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="D6" s="5" t="s">
+    </row>
+    <row r="23" spans="1:5" s="24" customFormat="1" ht="283.5">
+      <c r="A23" s="22"/>
+      <c r="B23" s="22"/>
+      <c r="C23" s="23" t="s">
+        <v>197</v>
+      </c>
+      <c r="D23" s="25" t="s">
+        <v>184</v>
+      </c>
+      <c r="E23" s="23"/>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24"/>
+      <c r="B24"/>
+      <c r="C24"/>
+      <c r="D24" s="14"/>
+      <c r="E24"/>
+    </row>
+    <row r="25" spans="1:5" s="24" customFormat="1" ht="27">
+      <c r="A25" s="19" t="s">
+        <v>129</v>
+      </c>
+      <c r="B25" s="22" t="s">
+        <v>130</v>
+      </c>
+      <c r="C25" s="23" t="s">
+        <v>185</v>
+      </c>
+      <c r="D25" s="23" t="s">
         <v>123</v>
       </c>
-      <c r="E6" s="5" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="B8" t="s">
-        <v>92</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="B10" t="s">
+      <c r="E25" s="23" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" s="24" customFormat="1" ht="162">
+      <c r="A26" s="22"/>
+      <c r="B26" s="22"/>
+      <c r="C26" s="23" t="s">
+        <v>131</v>
+      </c>
+      <c r="D26" s="23"/>
+      <c r="E26" s="23"/>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27"/>
+      <c r="B27"/>
+      <c r="C27"/>
+      <c r="D27" s="14"/>
+      <c r="E27"/>
+    </row>
+    <row r="28" spans="1:5" s="24" customFormat="1">
+      <c r="A28" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="B28" s="24" t="s">
+        <v>162</v>
+      </c>
+      <c r="C28" s="24" t="s">
+        <v>194</v>
+      </c>
+      <c r="D28" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="E28" s="24" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" s="24" customFormat="1" ht="108">
+      <c r="C29" s="28" t="s">
+        <v>165</v>
+      </c>
+      <c r="D29" s="22" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" s="24" customFormat="1">
+      <c r="A31" s="19" t="s">
+        <v>188</v>
+      </c>
+      <c r="B31" s="22" t="s">
+        <v>126</v>
+      </c>
+      <c r="C31" s="23" t="s">
+        <v>187</v>
+      </c>
+      <c r="D31" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="E31" s="23"/>
+    </row>
+    <row r="32" spans="1:5" s="24" customFormat="1" ht="409.5">
+      <c r="A32" s="22"/>
+      <c r="B32" s="22"/>
+      <c r="C32" s="23" t="s">
+        <v>186</v>
+      </c>
+      <c r="D32" s="23" t="s">
+        <v>154</v>
+      </c>
+      <c r="E32" s="23"/>
+    </row>
+    <row r="34" spans="1:5" s="24" customFormat="1">
+      <c r="A34" s="19" t="s">
+        <v>198</v>
+      </c>
+      <c r="B34" s="22" t="s">
+        <v>143</v>
+      </c>
+      <c r="C34" s="23" t="s">
+        <v>190</v>
+      </c>
+      <c r="D34" s="23" t="s">
+        <v>154</v>
+      </c>
+      <c r="E34" s="23"/>
+    </row>
+    <row r="35" spans="1:5" s="24" customFormat="1" ht="409.5">
+      <c r="A35" s="22"/>
+      <c r="B35" s="22"/>
+      <c r="C35" s="23" t="s">
+        <v>145</v>
+      </c>
+      <c r="D35" s="23" t="s">
+        <v>154</v>
+      </c>
+      <c r="E35" s="23"/>
+    </row>
+    <row r="37" spans="1:5" s="24" customFormat="1" ht="27">
+      <c r="A37" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="B37" s="22" t="s">
         <v>124</v>
       </c>
-      <c r="C10" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="27">
-      <c r="B12" t="s">
-        <v>125</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" ht="40.5">
-      <c r="A15" t="s">
-        <v>108</v>
-      </c>
-      <c r="B15" t="s">
-        <v>109</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="94.5">
-      <c r="A17" t="s">
-        <v>114</v>
-      </c>
-      <c r="B17" t="s">
-        <v>113</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>115</v>
-      </c>
+      <c r="C37" s="23" t="s">
+        <v>149</v>
+      </c>
+      <c r="D37" s="23" t="s">
+        <v>189</v>
+      </c>
+      <c r="E37" s="23"/>
+    </row>
+    <row r="38" spans="1:5" s="24" customFormat="1" ht="378">
+      <c r="A38" s="22"/>
+      <c r="B38" s="22"/>
+      <c r="C38" s="23" t="s">
+        <v>151</v>
+      </c>
+      <c r="D38" s="23" t="s">
+        <v>150</v>
+      </c>
+      <c r="E38" s="23"/>
+    </row>
+    <row r="40" spans="1:5" s="24" customFormat="1" ht="27">
+      <c r="A40" s="19" t="s">
+        <v>147</v>
+      </c>
+      <c r="B40" s="22" t="s">
+        <v>124</v>
+      </c>
+      <c r="C40" s="23" t="s">
+        <v>149</v>
+      </c>
+      <c r="D40" s="23" t="s">
+        <v>189</v>
+      </c>
+      <c r="E40" s="23"/>
+    </row>
+    <row r="41" spans="1:5" s="24" customFormat="1" ht="364.5">
+      <c r="A41" s="22"/>
+      <c r="B41" s="22"/>
+      <c r="C41" s="23" t="s">
+        <v>148</v>
+      </c>
+      <c r="D41" s="23" t="s">
+        <v>191</v>
+      </c>
+      <c r="E41" s="23"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E37"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
+  <cols>
+    <col min="1" max="1" width="18" style="13" customWidth="1"/>
+    <col min="2" max="2" width="24.25" style="14" customWidth="1"/>
+    <col min="3" max="3" width="24.375" style="13" customWidth="1"/>
+    <col min="4" max="4" width="50.875" style="13" customWidth="1"/>
+    <col min="5" max="5" width="50.75" style="13" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="14"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" s="34" customFormat="1">
+      <c r="A1" s="33" t="s">
+        <v>199</v>
+      </c>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="14" t="s">
+        <v>200</v>
+      </c>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+    </row>
+    <row r="4" spans="1:5" s="34" customFormat="1">
+      <c r="A4" s="33" t="s">
+        <v>201</v>
+      </c>
+      <c r="B4" s="34" t="s">
+        <v>202</v>
+      </c>
+      <c r="C4" s="33" t="s">
+        <v>203</v>
+      </c>
+      <c r="D4" s="33" t="s">
+        <v>204</v>
+      </c>
+      <c r="E4" s="33" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" s="26" customFormat="1" ht="189">
+      <c r="A5" s="27" t="s">
+        <v>109</v>
+      </c>
+      <c r="B5" s="26" t="s">
+        <v>108</v>
+      </c>
+      <c r="C5" s="27" t="s">
+        <v>107</v>
+      </c>
+      <c r="D5" s="27" t="s">
+        <v>207</v>
+      </c>
+      <c r="E5" s="27" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" s="26" customFormat="1" ht="202.5">
+      <c r="A7" s="27" t="s">
+        <v>110</v>
+      </c>
+      <c r="B7" s="26" t="s">
+        <v>111</v>
+      </c>
+      <c r="C7" s="27" t="s">
+        <v>112</v>
+      </c>
+      <c r="D7" s="27" t="s">
+        <v>209</v>
+      </c>
+      <c r="E7" s="27" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" s="26" customFormat="1" ht="409.5">
+      <c r="A8" s="27"/>
+      <c r="B8" s="26" t="s">
+        <v>120</v>
+      </c>
+      <c r="C8" s="27" t="s">
+        <v>121</v>
+      </c>
+      <c r="D8" s="27" t="s">
+        <v>210</v>
+      </c>
+      <c r="E8" s="27" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" s="26" customFormat="1" ht="216">
+      <c r="A9" s="27"/>
+      <c r="B9" s="26" t="s">
+        <v>113</v>
+      </c>
+      <c r="C9" s="27" t="s">
+        <v>114</v>
+      </c>
+      <c r="D9" s="27" t="s">
+        <v>212</v>
+      </c>
+      <c r="E9" s="27" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" s="26" customFormat="1">
+      <c r="A10" s="27"/>
+      <c r="B10" s="26" t="s">
+        <v>122</v>
+      </c>
+      <c r="C10" s="27" t="s">
+        <v>123</v>
+      </c>
+      <c r="D10" s="27" t="s">
+        <v>123</v>
+      </c>
+      <c r="E10" s="27" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" s="26" customFormat="1" ht="148.5">
+      <c r="A11" s="27"/>
+      <c r="B11" s="26" t="s">
+        <v>115</v>
+      </c>
+      <c r="C11" s="27" t="s">
+        <v>116</v>
+      </c>
+      <c r="D11" s="27" t="s">
+        <v>211</v>
+      </c>
+      <c r="E11" s="27" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" s="26" customFormat="1" ht="256.5">
+      <c r="A13" s="27" t="s">
+        <v>117</v>
+      </c>
+      <c r="B13" s="26" t="s">
+        <v>118</v>
+      </c>
+      <c r="C13" s="27" t="s">
+        <v>119</v>
+      </c>
+      <c r="D13" s="27" t="s">
+        <v>161</v>
+      </c>
+      <c r="E13" s="27" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" s="26" customFormat="1" ht="108">
+      <c r="A15" s="27" t="s">
+        <v>163</v>
+      </c>
+      <c r="B15" s="26" t="s">
+        <v>162</v>
+      </c>
+      <c r="C15" s="27" t="s">
+        <v>164</v>
+      </c>
+      <c r="D15" s="27" t="s">
+        <v>166</v>
+      </c>
+      <c r="E15" s="27" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" s="26" customFormat="1" ht="162">
+      <c r="A17" s="27" t="s">
+        <v>129</v>
+      </c>
+      <c r="B17" s="26" t="s">
+        <v>130</v>
+      </c>
+      <c r="C17" s="27" t="s">
+        <v>133</v>
+      </c>
+      <c r="D17" s="27" t="s">
+        <v>160</v>
+      </c>
+      <c r="E17" s="27" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" s="26" customFormat="1" ht="409.5">
+      <c r="A19" s="27" t="s">
+        <v>125</v>
+      </c>
+      <c r="B19" s="26" t="s">
+        <v>126</v>
+      </c>
+      <c r="C19" s="27" t="s">
+        <v>127</v>
+      </c>
+      <c r="D19" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="E19" s="27" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" s="26" customFormat="1">
+      <c r="A20" s="27"/>
+      <c r="C20" s="27" t="s">
+        <v>134</v>
+      </c>
+      <c r="D20" s="27" t="s">
+        <v>135</v>
+      </c>
+      <c r="E20" s="27" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" s="26" customFormat="1" ht="409.5">
+      <c r="A21" s="27"/>
+      <c r="C21" s="27" t="s">
+        <v>136</v>
+      </c>
+      <c r="D21" s="27" t="s">
+        <v>137</v>
+      </c>
+      <c r="E21" s="27" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" s="26" customFormat="1" ht="409.5">
+      <c r="A22" s="27"/>
+      <c r="C22" s="27" t="s">
+        <v>138</v>
+      </c>
+      <c r="D22" s="27" t="s">
+        <v>139</v>
+      </c>
+      <c r="E22" s="27" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" s="26" customFormat="1" ht="409.5">
+      <c r="A23" s="27"/>
+      <c r="C23" s="27" t="s">
+        <v>140</v>
+      </c>
+      <c r="D23" s="27" t="s">
+        <v>141</v>
+      </c>
+      <c r="E23" s="27"/>
+    </row>
+    <row r="24" spans="1:5" s="26" customFormat="1">
+      <c r="A24" s="27"/>
+      <c r="C24" s="27" t="s">
+        <v>152</v>
+      </c>
+      <c r="D24" s="27" t="s">
+        <v>153</v>
+      </c>
+      <c r="E24" s="27" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" s="26" customFormat="1" ht="409.5">
+      <c r="A28" s="27" t="s">
+        <v>142</v>
+      </c>
+      <c r="B28" s="26" t="s">
+        <v>143</v>
+      </c>
+      <c r="C28" s="27" t="s">
+        <v>144</v>
+      </c>
+      <c r="D28" s="27" t="s">
+        <v>145</v>
+      </c>
+      <c r="E28" s="27"/>
+    </row>
+    <row r="29" spans="1:5" s="26" customFormat="1">
+      <c r="A29" s="27"/>
+      <c r="C29" s="27" t="s">
+        <v>156</v>
+      </c>
+      <c r="D29" s="27"/>
+      <c r="E29" s="27"/>
+    </row>
+    <row r="30" spans="1:5" s="26" customFormat="1" ht="108">
+      <c r="A30" s="27"/>
+      <c r="C30" s="27" t="s">
+        <v>134</v>
+      </c>
+      <c r="D30" s="27" t="s">
+        <v>214</v>
+      </c>
+      <c r="E30" s="27" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" s="26" customFormat="1" ht="81">
+      <c r="A31" s="27"/>
+      <c r="C31" s="27" t="s">
+        <v>157</v>
+      </c>
+      <c r="D31" s="27" t="s">
+        <v>215</v>
+      </c>
+      <c r="E31" s="27" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" s="26" customFormat="1" ht="40.5">
+      <c r="A32" s="27"/>
+      <c r="C32" s="27" t="s">
+        <v>158</v>
+      </c>
+      <c r="D32" s="27" t="s">
+        <v>216</v>
+      </c>
+      <c r="E32" s="27" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" s="26" customFormat="1" ht="40.5">
+      <c r="A33" s="27"/>
+      <c r="C33" s="27" t="s">
+        <v>159</v>
+      </c>
+      <c r="D33" s="27" t="s">
+        <v>217</v>
+      </c>
+      <c r="E33" s="27" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" s="26" customFormat="1" ht="40.5">
+      <c r="A37" s="27" t="s">
+        <v>155</v>
+      </c>
+      <c r="B37" s="26" t="s">
+        <v>124</v>
+      </c>
+      <c r="C37" s="27" t="s">
+        <v>123</v>
+      </c>
+      <c r="D37" s="27" t="s">
+        <v>123</v>
+      </c>
+      <c r="E37" s="27" t="s">
+        <v>123</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/internal_doc/03.开发设计/OM_Agent接口.xlsx
+++ b/internal_doc/03.开发设计/OM_Agent接口.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14385" windowHeight="7485"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14385" windowHeight="7485" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="omagent需求（初稿）" sheetId="2" r:id="rId1"/>
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="219">
   <si>
     <t>检测host</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1522,10 +1522,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>参数</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>返回值</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1696,7 +1692,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="16">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1736,14 +1732,6 @@
       <color theme="1"/>
       <name val="宋体"/>
       <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <family val="2"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1808,16 +1796,8 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1837,6 +1817,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
@@ -1895,15 +1881,18 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="4">
+  <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1915,20 +1904,20 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="3" xfId="3" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" xfId="3" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1937,35 +1926,35 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="3" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="3" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="3" xfId="3" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="1" applyFont="1" applyAlignment="1">
@@ -1974,31 +1963,32 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="3" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="3" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="3" xfId="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="3" xfId="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="3" xfId="4" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="3" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="3" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="3" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="3" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="4">
+  <cellStyles count="5">
     <cellStyle name="20% - Accent3" xfId="3" builtinId="38"/>
+    <cellStyle name="40% - Accent3" xfId="4" builtinId="39"/>
     <cellStyle name="Accent3" xfId="2" builtinId="37"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Note" xfId="1" builtinId="10"/>
@@ -2727,7 +2717,7 @@
         <v>101</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="27">
@@ -3176,14 +3166,14 @@
       <c r="B4" s="34" t="s">
         <v>202</v>
       </c>
-      <c r="C4" s="33" t="s">
+      <c r="C4" s="35" t="s">
         <v>203</v>
       </c>
-      <c r="D4" s="33" t="s">
+      <c r="D4" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="E4" s="35" t="s">
         <v>204</v>
-      </c>
-      <c r="E4" s="33" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="5" spans="1:5" s="26" customFormat="1" ht="189">
@@ -3197,10 +3187,10 @@
         <v>107</v>
       </c>
       <c r="D5" s="27" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E5" s="27" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="7" spans="1:5" s="26" customFormat="1" ht="202.5">
@@ -3214,10 +3204,10 @@
         <v>112</v>
       </c>
       <c r="D7" s="27" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E7" s="27" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="8" spans="1:5" s="26" customFormat="1" ht="409.5">
@@ -3229,7 +3219,7 @@
         <v>121</v>
       </c>
       <c r="D8" s="27" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E8" s="27" t="s">
         <v>174</v>
@@ -3244,7 +3234,7 @@
         <v>114</v>
       </c>
       <c r="D9" s="27" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E9" s="27" t="s">
         <v>176</v>
@@ -3274,7 +3264,7 @@
         <v>116</v>
       </c>
       <c r="D11" s="27" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E11" s="27" t="s">
         <v>181</v>
@@ -3294,7 +3284,7 @@
         <v>161</v>
       </c>
       <c r="E13" s="27" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="15" spans="1:5" s="26" customFormat="1" ht="108">
@@ -3357,7 +3347,7 @@
         <v>135</v>
       </c>
       <c r="E20" s="27" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="21" spans="1:5" s="26" customFormat="1" ht="409.5">
@@ -3435,10 +3425,10 @@
         <v>134</v>
       </c>
       <c r="D30" s="27" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E30" s="27" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="31" spans="1:5" s="26" customFormat="1" ht="81">
@@ -3447,7 +3437,7 @@
         <v>157</v>
       </c>
       <c r="D31" s="27" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E31" s="27" t="s">
         <v>154</v>
@@ -3459,7 +3449,7 @@
         <v>158</v>
       </c>
       <c r="D32" s="27" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E32" s="27" t="s">
         <v>154</v>
@@ -3471,7 +3461,7 @@
         <v>159</v>
       </c>
       <c r="D33" s="27" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E33" s="27" t="s">
         <v>154</v>

--- a/internal_doc/03.开发设计/OM_Agent接口.xlsx
+++ b/internal_doc/03.开发设计/OM_Agent接口.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14385" windowHeight="7485" activeTab="3"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14385" windowHeight="7485" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="omagent需求（初稿）" sheetId="2" r:id="rId1"/>
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="226">
   <si>
     <t>检测host</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -528,93 +528,6 @@
   </si>
   <si>
     <t>createTempCoord.js，createCatalog.js， createCoord.js，createDataNode.js，createStandalone.js，removeStandalone.js，removeDataRG.js，removeCoordRG.js，removeCatalogRG.js，removeTempCoord.js，rollbackCatalog.js，rollbackCoord.js，rollbackDataNode.js</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{
-    "SdbUser": "sdbadmin", 
-    "SdbPasswd": "sdb     admin", 
-    "SdbUserGroup": "sdbadmin_group", 
-    "Config": [
-        {
-            "HostName": "rhel64-test8", 
-            "datagro     upname": "", 
-            "dbpath": "/sequoiadb/database/coord/11810", 
-            "svcname": "11810", 
-            "role": "coord     ", 
-            "diaglevel": "3", 
-            "hjbuf": "128", 
-            "logbuffsize": "1024", 
-            "logfilenum": "20", 
-            "logfilesz": "64", 
-            "maxprefpool": "200", 
-            "maxreplsync": "10", 
-            "numpagecleaners": "1", 
-            "numpreload": "0", 
-            "pagecleaninterval": "1000", 
-            "preferedinstance": "A", 
-            "sortbuf": "512", 
-            "syncstrategy": "no     ne", 
-            "transactionon": "false", 
-            "User": "root", 
-            "Passwd": "sequoiadb", 
-            "SshPort": "22"
-        }, 
-        {
-            "     HostName": "rhel64-test8", 
-            "datagroupname": "", 
-            "dbpath": "/sequoiadb/database/catalog/11820     ", 
-            "svcname": "11820", 
-            "role": "catalog", 
-            "diaglevel": "3", 
-            "hjbuf": "128", 
-            "logbuffsize": "     1024", 
-            "logfilenum": "20", 
-            "logfilesz": "64", 
-            "maxprefpool": "200", 
-            "maxreplsync": "10", 
-            "nu     mpagecleaners": "1", 
-            "numpreload": "0", 
-            "pagecleaninterval": "1000", 
-            "preferedinstance": "A", 
-            "sortbuf": "512", 
-            "syncstrategy": "none", 
-            "transactionon": "false", 
-            "User": "root", 
-            "Passw     d": "sequoiadb", 
-            "SshPort": "22"
-        }, 
-        {
-            "HostName": "rhel64-test8", 
-            "datagroupname": "group1", 
-            "dbpath": "/sequoiadb/database/data/11830", 
-            "svcname": "11830", 
-            "role": "data", 
-            "diaglevel": "3", 
-            "hjbuf": "128", 
-            "logbuffsize": "1024", 
-            "logfilenum": "20", 
-            "logfilesz": "64", 
-            "maxpre     fpool": "200", 
-            "maxreplsync": "10", 
-            "numpagecleaners": "1", 
-            "numpreload": "0", 
-            "pagecleanint     erval": "1000", 
-            "preferedinstance": "A", 
-            "sortbuf": "512", 
-            "syncstrategy": "none", 
-            "transact     ionon": "false", 
-            "User": "root", 
-            "Passwd": "sequoiadb", 
-            "SshPort": "22"
-        }
-    ], 
-    "ClusterName": "myCluster", 
-    "BusinessName": "myBusiness", 
-    "BusinessType": "sequoiadb", 
-    "DeployMod": "distri     bution", 
-    "TaskID": 3
-}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -732,41 +645,6 @@
   </si>
   <si>
     <t>createDataNode.js</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>var BUS_JSON = {
-    "InstallGroupName": "group1", 
-    "InstallHostName": "rhel64-test8", 
-    "InstallSvcName": "11830", 
-    "InstallPath": "/sequoiadb/database/data/11830", 
-    "InstallConfig": {
-        "role": "data", 
-        "diaglevel": "3", 
-        "hjbuf": "128", 
-        "logbuffsize": "1024", 
-        "logfilenum": "20", 
-        "logfilesz": "64", 
-        "maxprefpool": "200", 
-        "maxreplsync": "10", 
-        "numpagecleaners": "1", 
-        "numpreload": "0", 
-        "pagecleaninterval": "1000", 
-        "preferedinstance": "A", 
-        "sortbuf": "512", 
-        "syncstrategy": "none", 
-        "transactionon": "false"
-    }
-};var SYS_JSON = {
-    "VCoordSvcName": "10000", 
-    "SdbUser": "sdbadmin", 
-    "SdbPasswd": "sdbadmin", 
-    "SdbUserGroup": "sdbadmin_group", 
-    "User": "root", 
-    "Passwd": "sequoiadb", 
-    "SshPort": "22"
-}
-;</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1237,93 +1115,6 @@
   </si>
   <si>
     <t>{HostName,IP,User,Passwd,HostInfo:[HostName,IP]}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{
-    "SdbUser": "sdbadmin", 
-    "SdbPasswd": "sdbadmin", 
-    "SdbUserGroup": "sdbadmin_group", 
-    "Config": [
-        {
-            "HostName": "rhel64-test8", 
-            "datagroupname": "", 
-            "dbpath": "/sequoiadb/database/coord/11810", 
-            "svcname": "11810", 
-            "role": "coord     ", 
-            "diaglevel": "3", 
-            "hjbuf": "128", 
-            "logbuffsize": "1024", 
-            "logfilenum": "20", 
-            "logfilesz": "64", 
-            "maxprefpool": "200", 
-            "maxreplsync": "10", 
-            "numpagecleaners": "1", 
-            "numpreload": "0", 
-            "pagecleaninterval": "1000", 
-            "preferedinstance": "A", 
-            "sortbuf": "512", 
-            "syncstrategy": "none", 
-            "transactionon": "false", 
-            "User": "root", 
-            "Passwd": "sequoiadb", 
-            "SshPort": "22"
-        }, 
-        {
-            "HostName": "rhel64-test8", 
-            "datagroupname": "", 
-            "dbpath": "/sequoiadb/database/catalog/11820     ", 
-            "svcname": "11820", 
-            "role": "catalog", 
-            "diaglevel": "3", 
-            "hjbuf": "128", 
-            "logbuffsize": "1024", 
-            "logfilenum": "20", 
-            "logfilesz": "64", 
-            "maxprefpool": "200", 
-            "maxreplsync": "10", 
-            "numpagecleaners": "1", 
-            "numpreload": "0", 
-            "pagecleaninterval": "1000", 
-            "preferedinstance": "A", 
-            "sortbuf": "512", 
-            "syncstrategy": "none", 
-            "transactionon": "false", 
-            "User": "root", 
-            "Passwd": "sequoiadb", 
-            "SshPort": "22"
-        }, 
-        {
-            "HostName": "rhel64-test8", 
-            "datagroupname": "group1", 
-            "dbpath": "/sequoiadb/database/data/11830", 
-            "svcname": "11830", 
-            "role": "data", 
-            "diaglevel": "3", 
-            "hjbuf": "128", 
-            "logbuffsize": "1024", 
-            "logfilenum": "20", 
-            "logfilesz": "64", 
-            "maxprefpool": "200", 
-            "maxreplsync": "10", 
-            "numpagecleaners": "1", 
-            "numpreload": "0", 
-            "pagecleaninterval": "1000", 
-            "preferedinstance": "A", 
-            "sortbuf": "512", 
-            "syncstrategy": "none", 
-            "transactionon": "false", 
-            "User": "root", 
-            "Passwd": "sequoiadb", 
-            "SshPort": "22"
-        }
-    ], 
-    "ClusterName": "myCluster", 
-    "BusinessName": "myBusiness", 
-    "BusinessType": "sequoiadb", 
-    "DeployMod": "distribution", 
-    "TaskID": 3
-}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1685,6 +1476,303 @@
   </si>
   <si>
     <t>在安装失败后，需要清理环境，其中已安装的catalog无法删除</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+    "SdbUser": "sdbadmin", 
+    "SdbPasswd": "sdbadmin", 
+    "SdbUserGroup": "sdbadmin_group", 
+    "Config": [
+        {
+            "HostName": "rhel64-test8", 
+            "datagroupname": "", 
+            "dbpath": "/sequoiadb/database/coord/11810", 
+            "svcname": "11810", 
+            "role": "coord     ", 
+            "diaglevel": "3", 
+            "hjbuf": "128", 
+            "logbuffsize": "1024", 
+            "logfilenum": "20", 
+            "logfilesz": "64", 
+            "maxprefpool": "200", 
+            "maxreplsync": "10", 
+            "numpagecleaners": "1", 
+            "numpreload": "0", 
+            "pagecleaninterval": "1000", 
+            "preferedinstance": "A", 
+            "sortbuf": "512", 
+            "syncstrategy": "none", 
+            "transactionon": "false", 
+            "User": "root", 
+            "Passwd": "sequoiadb", 
+            "SshPort": "22"
+        }, 
+        {
+            "     HostName": "rhel64-test8", 
+            "datagroupname": "", 
+            "dbpath": "/sequoiadb/database/catalog/11820     ", 
+            "svcname": "11820", 
+            "role": "catalog", 
+            "diaglevel": "3", 
+            "hjbuf": "128", 
+            "logbuffsize": "     1024", 
+            "logfilenum": "20", 
+            "logfilesz": "64", 
+            "maxprefpool": "200", 
+            "maxreplsync": "10", 
+            "nu     mpagecleaners": "1", 
+            "numpreload": "0", 
+            "pagecleaninterval": "1000", 
+            "preferedinstance": "A", 
+            "sortbuf": "512", 
+            "syncstrategy": "none", 
+            "transactionon": "false", 
+            "User": "root", 
+            "Passw     d": "sequoiadb", 
+            "SshPort": "22"
+        }, 
+        {
+            "HostName": "rhel64-test8", 
+            "datagroupname": "group1", 
+            "dbpath": "/sequoiadb/database/data/11830", 
+            "svcname": "11830", 
+            "role": "data", 
+            "diaglevel": "3", 
+            "hjbuf": "128", 
+            "logbuffsize": "1024", 
+            "logfilenum": "20", 
+            "logfilesz": "64", 
+            "maxpre     fpool": "200", 
+            "maxreplsync": "10", 
+            "numpagecleaners": "1", 
+            "numpreload": "0", 
+            "pagecleanint     erval": "1000", 
+            "preferedinstance": "A", 
+            "sortbuf": "512", 
+            "syncstrategy": "none", 
+            "transact     ionon": "false", 
+            "User": "root", 
+            "Passwd": "sequoiadb", 
+            "SshPort": "22"
+        }
+    ], 
+    "ClusterName": "myCluster", 
+    "BusinessName": "myBusiness", 
+    "BusinessType": "sequoiadb", 
+    "DeployMod": "distribution", 
+    "TaskID": 3
+}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>var BUS_JSON = {
+    "InstallGroupName": "group1", 
+    "InstallHostName": "rhel64-test8", 
+    "InstallSvcName": "11830", 
+    "InstallPath": "/sequoiadb/database/data/11830", 
+    "InstallConfig": {
+        "role": "data", 
+        "diaglevel": "3", 
+        "hjbuf": "128", 
+        "logbuffsize": "1024", 
+        "logfilenum": "20", 
+        "logfilesz": "64", 
+        "maxprefpool": "200", 
+        "maxreplsync": "10", 
+        "numpagecleaners": "1", 
+        "numpreload": "0", 
+        "pagecleaninterval": "1000", 
+        "preferedinstance": "A", 
+        "sortbuf": "512", 
+        "syncstrategy": "none", 
+        "transactionon": "false"
+    }
+};var SYS_JSON = {
+    "VCoordSvcName": "10000", 
+    "SdbUser": "sdbadmin", 
+    "SdbPasswd": "sdbadmin", 
+    "SdbUserGroup": "sdbadmin_group", 
+    "User": "root", 
+    "Passwd": "sequoiadb", 
+    "SshPort": "22"
+}
+;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+    "SdbUser": "sdbadmin", 
+    "SdbPasswd": "sdbadmin", 
+    "SdbUserGroup": "sdbadmin_group", 
+    "Config": [
+        {
+            "HostName": "rhel64-test8", 
+            "datagroupname": "", 
+            "dbpath": "/sequoiadb/database/coord/11810", 
+            "svcname": "11810", 
+            "role": "coord     ", 
+            "diaglevel": "3", 
+            "hjbuf": "128", 
+            "logbuffsize": "1024", 
+            "logfilenum": "20", 
+            "logfilesz": "64", 
+            "maxprefpool": "200", 
+            "maxreplsync": "10", 
+            "numpagecleaners": "1", 
+            "numpreload": "0", 
+            "pagecleaninterval": "1000", 
+            "preferedinstance": "A", 
+            "sortbuf": "512", 
+            "syncstrategy": "none", 
+            "transactionon": "false", 
+            "User": "root", 
+            "Passwd": "sequoiadb", 
+            "SshPort": "22"
+        }, 
+        {
+            "HostName": "rhel64-test8", 
+            "datagroupname": "", 
+            "dbpath": "/sequoiadb/database/catalog/11820     ", 
+            "svcname": "11820", 
+            "role": "catalog", 
+            "diaglevel": "3", 
+            "hjbuf": "128", 
+            "logbuffsize": "1024", 
+            "logfilenum": "20", 
+            "logfilesz": "64", 
+            "maxprefpool": "200", 
+            "maxreplsync": "10", 
+            "numpagecleaners": "1", 
+            "numpreload": "0", 
+            "pagecleaninterval": "1000", 
+            "preferedinstance": "A", 
+            "sortbuf": "512", 
+            "syncstrategy": "none", 
+            "transactionon": "false", 
+            "User": "root", 
+            "Passwd": "sequoiadb", 
+            "SshPort": "22"
+        }, 
+        {
+            "HostName": "rhel64-test8", 
+            "datagroupname": "group1", 
+            "dbpath": "/sequoiadb/database/data/11830", 
+            "svcname": "11830", 
+            "role": "data", 
+            "diaglevel": "3", 
+            "hjbuf": "128", 
+            "logbuffsize": "1024", 
+            "logfilenum": "20", 
+            "logfilesz": "64", 
+            "maxprefpool": "200", 
+            "maxreplsync": "10", 
+            "numpagecleaners": "1", 
+            "numpreload": "0", 
+            "pagecleaninterval": "1000", 
+            "preferedinstance": "A", 
+            "sortbuf": "512", 
+            "syncstrategy": "none", 
+            "transactionon": "false", 
+            "User": "root", 
+            "Passwd": "sequoiadb", 
+            "SshPort": "22"
+        }
+    ], 
+    "ClusterName": "myCluster", 
+    "BusinessName": "myBusiness", 
+    "BusinessType": "sequoiadb", 
+    "DeployMod": "distribution", 
+    "TaskID": 3
+}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>由omsvc-&gt;omagent</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>由omagent-&gt;omsvc</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>查询task任务</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>$query task</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>未知</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">{
+    "TaskInfo": [
+        {
+            "TaskType": OM_TASK_ADD_BUS, // </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>建议使用一个枚举型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+            "TaskTypeStr": "add business", 
+            "TaskOwner":""
+            "TaskID": 1, 
+            "TaskStatus": "install", // </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>需要修改</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+            "Timestemp":""
+            "TaskDetail": {
+            // 原来的内容
+            }
+        }
+    ]
+}</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>待补充</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1896,7 +1984,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1985,6 +2073,16 @@
     <xf numFmtId="0" fontId="9" fillId="5" borderId="3" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="20% - Accent3" xfId="3" builtinId="38"/>
@@ -2717,7 +2815,7 @@
         <v>101</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="27">
@@ -2740,7 +2838,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E41"/>
+  <dimension ref="A1:E48"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="17.25" style="14" bestFit="1" customWidth="1"/>
@@ -2752,7 +2850,7 @@
   <sheetData>
     <row r="1" spans="1:5" s="32" customFormat="1">
       <c r="A1" s="30" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="B1" s="30"/>
       <c r="C1" s="31"/>
@@ -2761,7 +2859,7 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="14" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
     </row>
     <row r="4" spans="1:5" s="7" customFormat="1">
@@ -2779,349 +2877,408 @@
       </c>
       <c r="E4" s="10"/>
     </row>
-    <row r="5" spans="1:5" s="5" customFormat="1" ht="27">
-      <c r="A5" s="18" t="s">
+    <row r="5" spans="1:5" s="39" customFormat="1">
+      <c r="A5" s="36" t="s">
+        <v>219</v>
+      </c>
+      <c r="B5" s="37"/>
+      <c r="C5" s="38"/>
+      <c r="D5" s="38"/>
+      <c r="E5" s="38"/>
+    </row>
+    <row r="6" spans="1:5" s="5" customFormat="1" ht="27">
+      <c r="A6" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="B5" s="16" t="s">
+      <c r="B6" s="16" t="s">
         <v>108</v>
       </c>
-      <c r="C5" s="11" t="s">
-        <v>169</v>
-      </c>
-      <c r="D5" s="11" t="s">
-        <v>170</v>
-      </c>
-      <c r="E5" s="11" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" s="5" customFormat="1" ht="162">
-      <c r="A6" s="16"/>
-      <c r="B6" s="16"/>
       <c r="C6" s="11" t="s">
         <v>167</v>
       </c>
       <c r="D6" s="11" t="s">
         <v>168</v>
       </c>
-      <c r="E6" s="11"/>
-    </row>
-    <row r="8" spans="1:5" s="5" customFormat="1" ht="27">
-      <c r="A8" s="18" t="s">
+      <c r="E6" s="11" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" s="5" customFormat="1" ht="162">
+      <c r="A7" s="16"/>
+      <c r="B7" s="16"/>
+      <c r="C7" s="11" t="s">
+        <v>165</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>166</v>
+      </c>
+      <c r="E7" s="11"/>
+    </row>
+    <row r="9" spans="1:5" s="5" customFormat="1" ht="27">
+      <c r="A9" s="18" t="s">
         <v>90</v>
       </c>
-      <c r="B8" s="16" t="s">
+      <c r="B9" s="16" t="s">
         <v>111</v>
       </c>
-      <c r="C8" s="11" t="s">
+      <c r="C9" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>168</v>
+      </c>
+      <c r="E9" s="11" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" s="5" customFormat="1" ht="162">
+      <c r="A10" s="16"/>
+      <c r="B10" s="16"/>
+      <c r="C10" s="11" t="s">
+        <v>175</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="E10" s="11"/>
+    </row>
+    <row r="12" spans="1:5" s="6" customFormat="1" ht="27">
+      <c r="A12" s="17"/>
+      <c r="B12" s="17" t="s">
+        <v>113</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="E12" s="11" t="s">
         <v>171</v>
       </c>
-      <c r="D8" s="11" t="s">
-        <v>170</v>
-      </c>
-      <c r="E8" s="11" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" s="5" customFormat="1" ht="162">
-      <c r="A9" s="16"/>
-      <c r="B9" s="16"/>
-      <c r="C9" s="11" t="s">
+    </row>
+    <row r="13" spans="1:5" s="6" customFormat="1" ht="162">
+      <c r="A13" s="11"/>
+      <c r="B13" s="11"/>
+      <c r="C13" s="29" t="s">
+        <v>192</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>174</v>
+      </c>
+      <c r="E13" s="11"/>
+    </row>
+    <row r="15" spans="1:5" s="5" customFormat="1">
+      <c r="A15" s="18"/>
+      <c r="B15" s="18" t="s">
+        <v>120</v>
+      </c>
+      <c r="C15" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="D15" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="E15" s="11" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" s="5" customFormat="1" ht="409.5">
+      <c r="A16" s="16"/>
+      <c r="B16" s="16"/>
+      <c r="C16" s="29" t="s">
+        <v>193</v>
+      </c>
+      <c r="D16" s="11" t="s">
+        <v>172</v>
+      </c>
+      <c r="E16" s="11"/>
+    </row>
+    <row r="18" spans="1:5" s="9" customFormat="1">
+      <c r="A18" s="19"/>
+      <c r="B18" s="19" t="s">
         <v>177</v>
       </c>
-      <c r="D9" s="11" t="s">
+      <c r="C18" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="D18" s="12"/>
+      <c r="E18" s="12" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" s="9" customFormat="1" ht="27">
+      <c r="A20" s="19"/>
+      <c r="B20" s="19" t="s">
+        <v>115</v>
+      </c>
+      <c r="C20" s="23" t="s">
+        <v>167</v>
+      </c>
+      <c r="D20" s="12" t="s">
         <v>178</v>
       </c>
-      <c r="E9" s="11"/>
-    </row>
-    <row r="11" spans="1:5" s="6" customFormat="1" ht="27">
-      <c r="A11" s="17"/>
-      <c r="B11" s="17" t="s">
-        <v>113</v>
-      </c>
-      <c r="C11" s="11" t="s">
+      <c r="E20" s="12" t="s">
         <v>171</v>
       </c>
-      <c r="D11" s="11" t="s">
-        <v>172</v>
-      </c>
-      <c r="E11" s="11" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" s="6" customFormat="1" ht="162">
-      <c r="A12" s="11"/>
-      <c r="B12" s="11"/>
-      <c r="C12" s="29" t="s">
+    </row>
+    <row r="21" spans="1:5" s="9" customFormat="1" ht="162">
+      <c r="A21" s="21"/>
+      <c r="B21" s="21"/>
+      <c r="C21" s="23" t="s">
+        <v>192</v>
+      </c>
+      <c r="D21" s="12" t="s">
+        <v>179</v>
+      </c>
+      <c r="E21" s="12"/>
+    </row>
+    <row r="23" spans="1:5" s="24" customFormat="1" ht="40.5">
+      <c r="A23" s="19" t="s">
+        <v>98</v>
+      </c>
+      <c r="B23" s="22" t="s">
+        <v>118</v>
+      </c>
+      <c r="C23" s="23" t="s">
+        <v>181</v>
+      </c>
+      <c r="D23" s="23" t="s">
+        <v>100</v>
+      </c>
+      <c r="E23" s="23" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" s="24" customFormat="1" ht="283.5">
+      <c r="A24" s="22"/>
+      <c r="B24" s="22"/>
+      <c r="C24" s="23" t="s">
+        <v>194</v>
+      </c>
+      <c r="D24" s="25" t="s">
+        <v>182</v>
+      </c>
+      <c r="E24" s="23"/>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25"/>
+      <c r="B25"/>
+      <c r="C25"/>
+      <c r="D25" s="14"/>
+      <c r="E25"/>
+    </row>
+    <row r="26" spans="1:5" s="24" customFormat="1" ht="27">
+      <c r="A26" s="19" t="s">
+        <v>128</v>
+      </c>
+      <c r="B26" s="22" t="s">
+        <v>129</v>
+      </c>
+      <c r="C26" s="23" t="s">
+        <v>183</v>
+      </c>
+      <c r="D26" s="23" t="s">
+        <v>123</v>
+      </c>
+      <c r="E26" s="23" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" s="24" customFormat="1" ht="162">
+      <c r="A27" s="22"/>
+      <c r="B27" s="22"/>
+      <c r="C27" s="23" t="s">
+        <v>130</v>
+      </c>
+      <c r="D27" s="23"/>
+      <c r="E27" s="23"/>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28"/>
+      <c r="B28"/>
+      <c r="C28"/>
+      <c r="D28" s="14"/>
+      <c r="E28"/>
+    </row>
+    <row r="29" spans="1:5" s="24" customFormat="1">
+      <c r="A29" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="B29" s="24" t="s">
+        <v>160</v>
+      </c>
+      <c r="C29" s="24" t="s">
+        <v>191</v>
+      </c>
+      <c r="D29" s="22" t="s">
+        <v>152</v>
+      </c>
+      <c r="E29" s="24" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" s="24" customFormat="1" ht="108">
+      <c r="C30" s="28" t="s">
+        <v>163</v>
+      </c>
+      <c r="D30" s="22" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" s="24" customFormat="1">
+      <c r="A32" s="19" t="s">
+        <v>185</v>
+      </c>
+      <c r="B32" s="22" t="s">
+        <v>126</v>
+      </c>
+      <c r="C32" s="23" t="s">
+        <v>184</v>
+      </c>
+      <c r="D32" s="22" t="s">
+        <v>152</v>
+      </c>
+      <c r="E32" s="23"/>
+    </row>
+    <row r="33" spans="1:5" s="24" customFormat="1" ht="409.5">
+      <c r="A33" s="22"/>
+      <c r="B33" s="22"/>
+      <c r="C33" s="23" t="s">
+        <v>218</v>
+      </c>
+      <c r="D33" s="23" t="s">
+        <v>152</v>
+      </c>
+      <c r="E33" s="23"/>
+    </row>
+    <row r="35" spans="1:5" s="24" customFormat="1">
+      <c r="A35" s="19" t="s">
         <v>195</v>
       </c>
-      <c r="D12" s="11" t="s">
-        <v>176</v>
-      </c>
-      <c r="E12" s="11"/>
-    </row>
-    <row r="14" spans="1:5" s="5" customFormat="1">
-      <c r="A14" s="18"/>
-      <c r="B14" s="18" t="s">
-        <v>120</v>
-      </c>
-      <c r="C14" s="11" t="s">
-        <v>175</v>
-      </c>
-      <c r="D14" s="11" t="s">
-        <v>97</v>
-      </c>
-      <c r="E14" s="11" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" s="5" customFormat="1" ht="409.5">
-      <c r="A15" s="16"/>
-      <c r="B15" s="16"/>
-      <c r="C15" s="29" t="s">
-        <v>196</v>
-      </c>
-      <c r="D15" s="11" t="s">
-        <v>174</v>
-      </c>
-      <c r="E15" s="11"/>
-    </row>
-    <row r="17" spans="1:5" s="9" customFormat="1">
-      <c r="A17" s="19"/>
-      <c r="B17" s="19" t="s">
-        <v>179</v>
-      </c>
-      <c r="C17" s="12" t="s">
-        <v>154</v>
-      </c>
-      <c r="D17" s="12"/>
-      <c r="E17" s="12" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" s="9" customFormat="1" ht="27">
-      <c r="A19" s="19"/>
-      <c r="B19" s="19" t="s">
-        <v>115</v>
-      </c>
-      <c r="C19" s="23" t="s">
-        <v>169</v>
-      </c>
-      <c r="D19" s="12" t="s">
-        <v>180</v>
-      </c>
-      <c r="E19" s="12" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" s="9" customFormat="1" ht="162">
-      <c r="A20" s="21"/>
-      <c r="B20" s="21"/>
-      <c r="C20" s="23" t="s">
-        <v>195</v>
-      </c>
-      <c r="D20" s="12" t="s">
-        <v>181</v>
-      </c>
-      <c r="E20" s="12"/>
-    </row>
-    <row r="22" spans="1:5" s="24" customFormat="1" ht="40.5">
-      <c r="A22" s="19" t="s">
-        <v>98</v>
-      </c>
-      <c r="B22" s="22" t="s">
-        <v>118</v>
-      </c>
-      <c r="C22" s="23" t="s">
-        <v>183</v>
-      </c>
-      <c r="D22" s="23" t="s">
-        <v>100</v>
-      </c>
-      <c r="E22" s="23" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" s="24" customFormat="1" ht="283.5">
-      <c r="A23" s="22"/>
-      <c r="B23" s="22"/>
-      <c r="C23" s="23" t="s">
-        <v>197</v>
-      </c>
-      <c r="D23" s="25" t="s">
-        <v>184</v>
-      </c>
-      <c r="E23" s="23"/>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24"/>
-      <c r="B24"/>
-      <c r="C24"/>
-      <c r="D24" s="14"/>
-      <c r="E24"/>
-    </row>
-    <row r="25" spans="1:5" s="24" customFormat="1" ht="27">
-      <c r="A25" s="19" t="s">
-        <v>129</v>
-      </c>
-      <c r="B25" s="22" t="s">
-        <v>130</v>
-      </c>
-      <c r="C25" s="23" t="s">
-        <v>185</v>
-      </c>
-      <c r="D25" s="23" t="s">
-        <v>123</v>
-      </c>
-      <c r="E25" s="23" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" s="24" customFormat="1" ht="162">
-      <c r="A26" s="22"/>
-      <c r="B26" s="22"/>
-      <c r="C26" s="23" t="s">
-        <v>131</v>
-      </c>
-      <c r="D26" s="23"/>
-      <c r="E26" s="23"/>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27"/>
-      <c r="B27"/>
-      <c r="C27"/>
-      <c r="D27" s="14"/>
-      <c r="E27"/>
-    </row>
-    <row r="28" spans="1:5" s="24" customFormat="1">
-      <c r="A28" s="8" t="s">
-        <v>192</v>
-      </c>
-      <c r="B28" s="24" t="s">
-        <v>162</v>
-      </c>
-      <c r="C28" s="24" t="s">
-        <v>194</v>
-      </c>
-      <c r="D28" s="22" t="s">
-        <v>154</v>
-      </c>
-      <c r="E28" s="24" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" s="24" customFormat="1" ht="108">
-      <c r="C29" s="28" t="s">
-        <v>165</v>
-      </c>
-      <c r="D29" s="22" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" s="24" customFormat="1">
-      <c r="A31" s="19" t="s">
+      <c r="B35" s="22" t="s">
+        <v>141</v>
+      </c>
+      <c r="C35" s="23" t="s">
+        <v>187</v>
+      </c>
+      <c r="D35" s="23" t="s">
+        <v>152</v>
+      </c>
+      <c r="E35" s="23"/>
+    </row>
+    <row r="36" spans="1:5" s="24" customFormat="1" ht="409.5">
+      <c r="A36" s="22"/>
+      <c r="B36" s="22"/>
+      <c r="C36" s="23" t="s">
+        <v>143</v>
+      </c>
+      <c r="D36" s="23" t="s">
+        <v>152</v>
+      </c>
+      <c r="E36" s="23"/>
+    </row>
+    <row r="38" spans="1:5" s="24" customFormat="1" ht="27">
+      <c r="A38" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="B38" s="22" t="s">
+        <v>124</v>
+      </c>
+      <c r="C38" s="23" t="s">
+        <v>147</v>
+      </c>
+      <c r="D38" s="23" t="s">
+        <v>186</v>
+      </c>
+      <c r="E38" s="23"/>
+    </row>
+    <row r="39" spans="1:5" s="24" customFormat="1" ht="378">
+      <c r="A39" s="22"/>
+      <c r="B39" s="22"/>
+      <c r="C39" s="23" t="s">
+        <v>149</v>
+      </c>
+      <c r="D39" s="23" t="s">
+        <v>148</v>
+      </c>
+      <c r="E39" s="23"/>
+    </row>
+    <row r="41" spans="1:5" s="24" customFormat="1" ht="27">
+      <c r="A41" s="19" t="s">
+        <v>145</v>
+      </c>
+      <c r="B41" s="22" t="s">
+        <v>124</v>
+      </c>
+      <c r="C41" s="23" t="s">
+        <v>147</v>
+      </c>
+      <c r="D41" s="23" t="s">
+        <v>186</v>
+      </c>
+      <c r="E41" s="23"/>
+    </row>
+    <row r="42" spans="1:5" s="24" customFormat="1" ht="364.5">
+      <c r="A42" s="22"/>
+      <c r="B42" s="22"/>
+      <c r="C42" s="23" t="s">
+        <v>146</v>
+      </c>
+      <c r="D42" s="23" t="s">
         <v>188</v>
       </c>
-      <c r="B31" s="22" t="s">
-        <v>126</v>
-      </c>
-      <c r="C31" s="23" t="s">
-        <v>187</v>
-      </c>
-      <c r="D31" s="22" t="s">
-        <v>154</v>
-      </c>
-      <c r="E31" s="23"/>
-    </row>
-    <row r="32" spans="1:5" s="24" customFormat="1" ht="409.5">
-      <c r="A32" s="22"/>
-      <c r="B32" s="22"/>
-      <c r="C32" s="23" t="s">
-        <v>186</v>
-      </c>
-      <c r="D32" s="23" t="s">
-        <v>154</v>
-      </c>
-      <c r="E32" s="23"/>
-    </row>
-    <row r="34" spans="1:5" s="24" customFormat="1">
-      <c r="A34" s="19" t="s">
-        <v>198</v>
-      </c>
-      <c r="B34" s="22" t="s">
-        <v>143</v>
-      </c>
-      <c r="C34" s="23" t="s">
-        <v>190</v>
-      </c>
-      <c r="D34" s="23" t="s">
-        <v>154</v>
-      </c>
-      <c r="E34" s="23"/>
-    </row>
-    <row r="35" spans="1:5" s="24" customFormat="1" ht="409.5">
-      <c r="A35" s="22"/>
-      <c r="B35" s="22"/>
-      <c r="C35" s="23" t="s">
-        <v>145</v>
-      </c>
-      <c r="D35" s="23" t="s">
-        <v>154</v>
-      </c>
-      <c r="E35" s="23"/>
-    </row>
-    <row r="37" spans="1:5" s="24" customFormat="1" ht="27">
-      <c r="A37" s="19" t="s">
-        <v>146</v>
-      </c>
-      <c r="B37" s="22" t="s">
-        <v>124</v>
-      </c>
-      <c r="C37" s="23" t="s">
-        <v>149</v>
-      </c>
-      <c r="D37" s="23" t="s">
-        <v>189</v>
-      </c>
-      <c r="E37" s="23"/>
-    </row>
-    <row r="38" spans="1:5" s="24" customFormat="1" ht="378">
-      <c r="A38" s="22"/>
-      <c r="B38" s="22"/>
-      <c r="C38" s="23" t="s">
-        <v>151</v>
-      </c>
-      <c r="D38" s="23" t="s">
-        <v>150</v>
-      </c>
-      <c r="E38" s="23"/>
-    </row>
-    <row r="40" spans="1:5" s="24" customFormat="1" ht="27">
-      <c r="A40" s="19" t="s">
-        <v>147</v>
-      </c>
-      <c r="B40" s="22" t="s">
-        <v>124</v>
-      </c>
-      <c r="C40" s="23" t="s">
-        <v>149</v>
-      </c>
-      <c r="D40" s="23" t="s">
-        <v>189</v>
-      </c>
-      <c r="E40" s="23"/>
-    </row>
-    <row r="41" spans="1:5" s="24" customFormat="1" ht="364.5">
-      <c r="A41" s="22"/>
-      <c r="B41" s="22"/>
-      <c r="C41" s="23" t="s">
-        <v>148</v>
-      </c>
-      <c r="D41" s="23" t="s">
-        <v>191</v>
-      </c>
-      <c r="E41" s="23"/>
+      <c r="E42" s="23"/>
+    </row>
+    <row r="45" spans="1:5" s="7" customFormat="1">
+      <c r="A45" s="20" t="s">
+        <v>91</v>
+      </c>
+      <c r="B45" s="15" t="s">
+        <v>92</v>
+      </c>
+      <c r="C45" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="D45" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="E45" s="10"/>
+    </row>
+    <row r="46" spans="1:5" s="39" customFormat="1">
+      <c r="A46" s="36" t="s">
+        <v>220</v>
+      </c>
+      <c r="B46" s="37"/>
+      <c r="C46" s="38"/>
+      <c r="D46" s="38"/>
+      <c r="E46" s="38"/>
+    </row>
+    <row r="47" spans="1:5" s="24" customFormat="1" ht="216">
+      <c r="A47" s="19" t="s">
+        <v>221</v>
+      </c>
+      <c r="B47" s="22" t="s">
+        <v>222</v>
+      </c>
+      <c r="C47" s="25" t="s">
+        <v>223</v>
+      </c>
+      <c r="D47" s="23" t="s">
+        <v>224</v>
+      </c>
+      <c r="E47" s="23"/>
+    </row>
+    <row r="48" spans="1:5" s="24" customFormat="1">
+      <c r="A48" s="22"/>
+      <c r="B48" s="22"/>
+      <c r="C48" s="25" t="s">
+        <v>223</v>
+      </c>
+      <c r="D48" s="25" t="s">
+        <v>225</v>
+      </c>
+      <c r="E48" s="23"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -3145,7 +3302,7 @@
   <sheetData>
     <row r="1" spans="1:5" s="34" customFormat="1">
       <c r="A1" s="33" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="C1" s="35"/>
       <c r="D1" s="35"/>
@@ -3153,7 +3310,7 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="14" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="C2" s="14"/>
       <c r="D2" s="14"/>
@@ -3161,19 +3318,19 @@
     </row>
     <row r="4" spans="1:5" s="34" customFormat="1">
       <c r="A4" s="33" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="B4" s="34" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="C4" s="35" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="D4" s="35" t="s">
         <v>93</v>
       </c>
       <c r="E4" s="35" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
     </row>
     <row r="5" spans="1:5" s="26" customFormat="1" ht="189">
@@ -3187,10 +3344,10 @@
         <v>107</v>
       </c>
       <c r="D5" s="27" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="E5" s="27" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
     </row>
     <row r="7" spans="1:5" s="26" customFormat="1" ht="202.5">
@@ -3204,10 +3361,10 @@
         <v>112</v>
       </c>
       <c r="D7" s="27" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="E7" s="27" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
     </row>
     <row r="8" spans="1:5" s="26" customFormat="1" ht="409.5">
@@ -3219,10 +3376,10 @@
         <v>121</v>
       </c>
       <c r="D8" s="27" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="E8" s="27" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="9" spans="1:5" s="26" customFormat="1" ht="216">
@@ -3234,10 +3391,10 @@
         <v>114</v>
       </c>
       <c r="D9" s="27" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="E9" s="27" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="10" spans="1:5" s="26" customFormat="1">
@@ -3264,10 +3421,10 @@
         <v>116</v>
       </c>
       <c r="D11" s="27" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="E11" s="27" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="13" spans="1:5" s="26" customFormat="1" ht="256.5">
@@ -3281,44 +3438,44 @@
         <v>119</v>
       </c>
       <c r="D13" s="27" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E13" s="27" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
     </row>
     <row r="15" spans="1:5" s="26" customFormat="1" ht="108">
       <c r="A15" s="27" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B15" s="26" t="s">
+        <v>160</v>
+      </c>
+      <c r="C15" s="27" t="s">
         <v>162</v>
       </c>
-      <c r="C15" s="27" t="s">
+      <c r="D15" s="27" t="s">
         <v>164</v>
       </c>
-      <c r="D15" s="27" t="s">
-        <v>166</v>
-      </c>
       <c r="E15" s="27" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="17" spans="1:5" s="26" customFormat="1" ht="162">
       <c r="A17" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="B17" s="26" t="s">
         <v>129</v>
       </c>
-      <c r="B17" s="26" t="s">
-        <v>130</v>
-      </c>
       <c r="C17" s="27" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D17" s="27" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="E17" s="27" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="19" spans="1:5" s="26" customFormat="1" ht="409.5">
@@ -3332,7 +3489,7 @@
         <v>127</v>
       </c>
       <c r="D19" s="27" t="s">
-        <v>128</v>
+        <v>216</v>
       </c>
       <c r="E19" s="27" t="s">
         <v>123</v>
@@ -3341,80 +3498,80 @@
     <row r="20" spans="1:5" s="26" customFormat="1">
       <c r="A20" s="27"/>
       <c r="C20" s="27" t="s">
+        <v>133</v>
+      </c>
+      <c r="D20" s="27" t="s">
         <v>134</v>
       </c>
-      <c r="D20" s="27" t="s">
-        <v>135</v>
-      </c>
       <c r="E20" s="27" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
     </row>
     <row r="21" spans="1:5" s="26" customFormat="1" ht="409.5">
       <c r="A21" s="27"/>
       <c r="C21" s="27" t="s">
+        <v>135</v>
+      </c>
+      <c r="D21" s="27" t="s">
         <v>136</v>
       </c>
-      <c r="D21" s="27" t="s">
-        <v>137</v>
-      </c>
       <c r="E21" s="27" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="22" spans="1:5" s="26" customFormat="1" ht="409.5">
       <c r="A22" s="27"/>
       <c r="C22" s="27" t="s">
+        <v>137</v>
+      </c>
+      <c r="D22" s="27" t="s">
         <v>138</v>
       </c>
-      <c r="D22" s="27" t="s">
-        <v>139</v>
-      </c>
       <c r="E22" s="27" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="23" spans="1:5" s="26" customFormat="1" ht="409.5">
       <c r="A23" s="27"/>
       <c r="C23" s="27" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D23" s="27" t="s">
-        <v>141</v>
+        <v>217</v>
       </c>
       <c r="E23" s="27"/>
     </row>
     <row r="24" spans="1:5" s="26" customFormat="1">
       <c r="A24" s="27"/>
       <c r="C24" s="27" t="s">
+        <v>150</v>
+      </c>
+      <c r="D24" s="27" t="s">
+        <v>151</v>
+      </c>
+      <c r="E24" s="27" t="s">
         <v>152</v>
-      </c>
-      <c r="D24" s="27" t="s">
-        <v>153</v>
-      </c>
-      <c r="E24" s="27" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="28" spans="1:5" s="26" customFormat="1" ht="409.5">
       <c r="A28" s="27" t="s">
+        <v>140</v>
+      </c>
+      <c r="B28" s="26" t="s">
+        <v>141</v>
+      </c>
+      <c r="C28" s="27" t="s">
         <v>142</v>
       </c>
-      <c r="B28" s="26" t="s">
+      <c r="D28" s="27" t="s">
         <v>143</v>
-      </c>
-      <c r="C28" s="27" t="s">
-        <v>144</v>
-      </c>
-      <c r="D28" s="27" t="s">
-        <v>145</v>
       </c>
       <c r="E28" s="27"/>
     </row>
     <row r="29" spans="1:5" s="26" customFormat="1">
       <c r="A29" s="27"/>
       <c r="C29" s="27" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D29" s="27"/>
       <c r="E29" s="27"/>
@@ -3422,54 +3579,54 @@
     <row r="30" spans="1:5" s="26" customFormat="1" ht="108">
       <c r="A30" s="27"/>
       <c r="C30" s="27" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D30" s="27" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="E30" s="27" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
     </row>
     <row r="31" spans="1:5" s="26" customFormat="1" ht="81">
       <c r="A31" s="27"/>
       <c r="C31" s="27" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D31" s="27" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="E31" s="27" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="32" spans="1:5" s="26" customFormat="1" ht="40.5">
       <c r="A32" s="27"/>
       <c r="C32" s="27" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D32" s="27" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="E32" s="27" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="33" spans="1:5" s="26" customFormat="1" ht="40.5">
       <c r="A33" s="27"/>
       <c r="C33" s="27" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D33" s="27" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="E33" s="27" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="37" spans="1:5" s="26" customFormat="1" ht="40.5">
       <c r="A37" s="27" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B37" s="26" t="s">
         <v>124</v>

--- a/internal_doc/03.开发设计/OM_Agent接口.xlsx
+++ b/internal_doc/03.开发设计/OM_Agent接口.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="231">
   <si>
     <t>检测host</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -416,10 +416,6 @@
   </si>
   <si>
     <t>全部安装成功才返回成功，否则返回失败并由agent将环境清理干净</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{rc, TransactionID}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1198,6 +1194,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -1233,6 +1230,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -1708,11 +1706,128 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>待补充</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>$check host</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>发给本地Agent，由本地Agent通过oma练到远端获取</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{rc, TransactionID} // outdated, need to check</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+    "HostInfo": [
+        {
+            "errno": 0, 
+            "detail": "", 
+            "IP": "192.168.20.165"
+        }
+    ]
+}+D27</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+    "HostInfo": [
+        {
+            "IP": "192.168.20.165", 
+            "HostName": "rhel64-test8", 
+            "OS": {
+                "Distributor": "RedHatEnterpriseServer", 
+                "Release": "6.4", 
+                "Bit": 64
+            }, 
+            "OM": {
+                "HasInstalled": false, 
+                "Version": "", 
+                "Path": "", 
+                "Port": "", 
+                "Release": ""
+            }, 
+            "CPU": [
+                {
+                    "ID": "", 
+                    "Model": "Intel(R) Xeon(R) CPU E5-2620 0 ", 
+                    "Core": 2, 
+                    "Freq": "2.00GHz"
+                }
+            ], 
+            "Memory": {
+                "Model": "", 
+                "Size": 2887, 
+                "Free": 2310
+            }, 
+            "Disk": [
+                {
+                    "Name": "/dev/mapper/vg_rhel64test8-lv_root", 
+                    "Mount": "/", 
+                    "Size": 43659, 
+                    "Free": 39539, 
+                    "IsLocal": true
+                }, 
+                {
+                    "Name": "/dev/sda1", 
+                    "Mount": "/boot", 
+                    "Size": 460, 
+                    "Free": 423, 
+                    "IsLocal": true
+                }, 
+                {
+                    "Name": "//192.168.20.10/files", 
+                    "Mount": "/mnt", 
+                    "Size": 47837, 
+                    "Free": 5970, 
+                    "IsLocal": false
+                }
+            ], 
+            "Net": [
+                {
+                    "Name": "lo", 
+                    "Model": "", 
+                    "Bandwidth": "", 
+                    "IP": "127.0.0.1"
+                }, 
+                {
+                    "Name": "eth0", 
+                    "Model": "", 
+                    "Bandwidth": "", 
+                    "IP": "192.168.20.165"
+                }
+            ], 
+            "Port": [
+                {
+                    "Port": "", 
+                    "CanUse": false
+                }
+            ], 
+            "Service": [
+                {
+                    "Name": "", 
+                    "IsRunning": false, 
+                    "Version": ""
+                }
+            ], 
+            "Safety": {
+                "Name": "", 
+                "Context": "", 
+                "IsRunning": false
+            }
+        }
+    ]
+}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <r>
       <t xml:space="preserve">{
-    "TaskInfo": [
-        {
-            "TaskType": OM_TASK_ADD_BUS, // </t>
+    "TaskType": OM_TASK_ADD_HOST, // </t>
     </r>
     <r>
       <rPr>
@@ -1734,11 +1849,11 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">
-            "TaskTypeStr": "add business", 
-            "TaskOwner":""
-            "TaskID": 1, 
-            "TaskStatus": "install", // </t>
+      <t xml:space="preserve">, 
+    "TaskTypeStr": "add host", 
+    "TaskOwner": "", 
+    "TaskID": 1, 
+    "TaskStatus": "install", // </t>
     </r>
     <r>
       <rPr>
@@ -1761,18 +1876,51 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">
-            "Timestemp":""
-            "TaskDetail": {
-            // 原来的内容
-            }
-        }
-    ]
-}</t>
+    "Timestemp": "", 
+    "TaskDetail": { 
+    // </t>
     </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>待补充</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>原来的内容</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+    }
+}
+{
+    "TaskType": OM_TASK_ADD_BUS, // 建议使用一个枚举型, 
+    "TaskTypeStr": "add business", 
+    "TaskOwner": "", 
+    "TaskID": 2, 
+    "TaskStatus": "install", // 需要修改
+    "Timestemp": "", 
+    "TaskDetail": { 
+    // 原来的内容
+    }
+}
+...
+</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{HostName:"",AgentPort:""} // 是否需要修改</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1850,6 +1998,7 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1857,6 +2006,7 @@
       <sz val="11"/>
       <color theme="0"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -2801,32 +2951,32 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B1" t="s">
         <v>102</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>103</v>
-      </c>
-      <c r="C1" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="27">
       <c r="A2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="27">
       <c r="A3" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C3" s="4"/>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
   </sheetData>
@@ -2838,7 +2988,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E48"/>
+  <dimension ref="A1:E55"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="17.25" style="14" bestFit="1" customWidth="1"/>
@@ -2850,7 +3000,7 @@
   <sheetData>
     <row r="1" spans="1:5" s="32" customFormat="1">
       <c r="A1" s="30" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B1" s="30"/>
       <c r="C1" s="31"/>
@@ -2859,7 +3009,7 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="14" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="4" spans="1:5" s="7" customFormat="1">
@@ -2879,7 +3029,7 @@
     </row>
     <row r="5" spans="1:5" s="39" customFormat="1">
       <c r="A5" s="36" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B5" s="37"/>
       <c r="C5" s="38"/>
@@ -2891,13 +3041,13 @@
         <v>33</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C6" s="11" t="s">
+        <v>166</v>
+      </c>
+      <c r="D6" s="11" t="s">
         <v>167</v>
-      </c>
-      <c r="D6" s="11" t="s">
-        <v>168</v>
       </c>
       <c r="E6" s="11" t="s">
         <v>96</v>
@@ -2907,10 +3057,10 @@
       <c r="A7" s="16"/>
       <c r="B7" s="16"/>
       <c r="C7" s="11" t="s">
+        <v>164</v>
+      </c>
+      <c r="D7" s="11" t="s">
         <v>165</v>
-      </c>
-      <c r="D7" s="11" t="s">
-        <v>166</v>
       </c>
       <c r="E7" s="11"/>
     </row>
@@ -2919,13 +3069,13 @@
         <v>90</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E9" s="11" t="s">
         <v>95</v>
@@ -2935,46 +3085,46 @@
       <c r="A10" s="16"/>
       <c r="B10" s="16"/>
       <c r="C10" s="11" t="s">
+        <v>174</v>
+      </c>
+      <c r="D10" s="11" t="s">
         <v>175</v>
-      </c>
-      <c r="D10" s="11" t="s">
-        <v>176</v>
       </c>
       <c r="E10" s="11"/>
     </row>
     <row r="12" spans="1:5" s="6" customFormat="1" ht="27">
       <c r="A12" s="17"/>
       <c r="B12" s="17" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C12" s="11" t="s">
+        <v>168</v>
+      </c>
+      <c r="D12" s="11" t="s">
         <v>169</v>
       </c>
-      <c r="D12" s="11" t="s">
+      <c r="E12" s="11" t="s">
         <v>170</v>
-      </c>
-      <c r="E12" s="11" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="13" spans="1:5" s="6" customFormat="1" ht="162">
       <c r="A13" s="11"/>
       <c r="B13" s="11"/>
       <c r="C13" s="29" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E13" s="11"/>
     </row>
     <row r="15" spans="1:5" s="5" customFormat="1">
       <c r="A15" s="18"/>
       <c r="B15" s="18" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D15" s="11" t="s">
         <v>97</v>
@@ -2987,49 +3137,49 @@
       <c r="A16" s="16"/>
       <c r="B16" s="16"/>
       <c r="C16" s="29" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E16" s="11"/>
     </row>
     <row r="18" spans="1:5" s="9" customFormat="1">
       <c r="A18" s="19"/>
       <c r="B18" s="19" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D18" s="12"/>
       <c r="E18" s="12" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="20" spans="1:5" s="9" customFormat="1" ht="27">
       <c r="A20" s="19"/>
       <c r="B20" s="19" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C20" s="23" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="21" spans="1:5" s="9" customFormat="1" ht="162">
       <c r="A21" s="21"/>
       <c r="B21" s="21"/>
       <c r="C21" s="23" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>179</v>
+        <v>227</v>
       </c>
       <c r="E21" s="12"/>
     </row>
@@ -3038,13 +3188,13 @@
         <v>98</v>
       </c>
       <c r="B23" s="22" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C23" s="23" t="s">
-        <v>181</v>
-      </c>
-      <c r="D23" s="23" t="s">
-        <v>100</v>
+        <v>180</v>
+      </c>
+      <c r="D23" s="25" t="s">
+        <v>226</v>
       </c>
       <c r="E23" s="23" t="s">
         <v>99</v>
@@ -3054,10 +3204,10 @@
       <c r="A24" s="22"/>
       <c r="B24" s="22"/>
       <c r="C24" s="23" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D24" s="25" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E24" s="23"/>
     </row>
@@ -3070,26 +3220,26 @@
     </row>
     <row r="26" spans="1:5" s="24" customFormat="1" ht="27">
       <c r="A26" s="19" t="s">
+        <v>127</v>
+      </c>
+      <c r="B26" s="22" t="s">
         <v>128</v>
       </c>
-      <c r="B26" s="22" t="s">
-        <v>129</v>
-      </c>
       <c r="C26" s="23" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D26" s="23" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E26" s="23" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="27" spans="1:5" s="24" customFormat="1" ht="162">
       <c r="A27" s="22"/>
       <c r="B27" s="22"/>
       <c r="C27" s="23" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D27" s="23"/>
       <c r="E27" s="23"/>
@@ -3103,41 +3253,41 @@
     </row>
     <row r="29" spans="1:5" s="24" customFormat="1">
       <c r="A29" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="B29" s="24" t="s">
+        <v>159</v>
+      </c>
+      <c r="C29" s="24" t="s">
+        <v>190</v>
+      </c>
+      <c r="D29" s="22" t="s">
+        <v>151</v>
+      </c>
+      <c r="E29" s="24" t="s">
         <v>189</v>
-      </c>
-      <c r="B29" s="24" t="s">
-        <v>160</v>
-      </c>
-      <c r="C29" s="24" t="s">
-        <v>191</v>
-      </c>
-      <c r="D29" s="22" t="s">
-        <v>152</v>
-      </c>
-      <c r="E29" s="24" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="30" spans="1:5" s="24" customFormat="1" ht="108">
       <c r="C30" s="28" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D30" s="22" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="32" spans="1:5" s="24" customFormat="1">
       <c r="A32" s="19" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B32" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C32" s="23" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D32" s="22" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E32" s="23"/>
     </row>
@@ -3145,25 +3295,25 @@
       <c r="A33" s="22"/>
       <c r="B33" s="22"/>
       <c r="C33" s="23" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D33" s="23" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E33" s="23"/>
     </row>
     <row r="35" spans="1:5" s="24" customFormat="1">
       <c r="A35" s="19" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B35" s="22" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C35" s="23" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D35" s="23" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E35" s="23"/>
     </row>
@@ -3171,25 +3321,25 @@
       <c r="A36" s="22"/>
       <c r="B36" s="22"/>
       <c r="C36" s="23" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D36" s="23" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E36" s="23"/>
     </row>
     <row r="38" spans="1:5" s="24" customFormat="1" ht="27">
       <c r="A38" s="19" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B38" s="22" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C38" s="23" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D38" s="23" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E38" s="23"/>
     </row>
@@ -3197,25 +3347,25 @@
       <c r="A39" s="22"/>
       <c r="B39" s="22"/>
       <c r="C39" s="23" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D39" s="23" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E39" s="23"/>
     </row>
     <row r="41" spans="1:5" s="24" customFormat="1" ht="27">
       <c r="A41" s="19" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B41" s="22" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C41" s="23" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D41" s="23" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E41" s="23"/>
     </row>
@@ -3223,62 +3373,125 @@
       <c r="A42" s="22"/>
       <c r="B42" s="22"/>
       <c r="C42" s="23" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D42" s="23" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E42" s="23"/>
     </row>
-    <row r="45" spans="1:5" s="7" customFormat="1">
-      <c r="A45" s="20" t="s">
+    <row r="43" spans="1:5">
+      <c r="A43"/>
+      <c r="B43"/>
+      <c r="C43"/>
+      <c r="D43"/>
+      <c r="E43"/>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44"/>
+      <c r="B44"/>
+      <c r="C44"/>
+      <c r="D44"/>
+      <c r="E44"/>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45"/>
+      <c r="B45"/>
+      <c r="C45"/>
+      <c r="D45"/>
+      <c r="E45"/>
+    </row>
+    <row r="47" spans="1:5" s="5" customFormat="1" ht="27">
+      <c r="A47" s="18" t="s">
+        <v>90</v>
+      </c>
+      <c r="B47" s="16" t="s">
+        <v>224</v>
+      </c>
+      <c r="C47" s="11" t="s">
+        <v>168</v>
+      </c>
+      <c r="D47" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="E47" s="11" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" s="5" customFormat="1" ht="409.5">
+      <c r="A48" s="16"/>
+      <c r="B48" s="16"/>
+      <c r="C48" s="11" t="s">
+        <v>174</v>
+      </c>
+      <c r="D48" s="11" t="s">
+        <v>228</v>
+      </c>
+      <c r="E48" s="11"/>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49"/>
+      <c r="B49"/>
+      <c r="C49"/>
+      <c r="D49"/>
+      <c r="E49"/>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50"/>
+      <c r="B50"/>
+      <c r="C50"/>
+      <c r="D50"/>
+      <c r="E50"/>
+    </row>
+    <row r="52" spans="1:5" s="7" customFormat="1">
+      <c r="A52" s="20" t="s">
         <v>91</v>
       </c>
-      <c r="B45" s="15" t="s">
+      <c r="B52" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="C45" s="10" t="s">
+      <c r="C52" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="D45" s="10" t="s">
+      <c r="D52" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="E45" s="10"/>
-    </row>
-    <row r="46" spans="1:5" s="39" customFormat="1">
-      <c r="A46" s="36" t="s">
+      <c r="E52" s="10"/>
+    </row>
+    <row r="53" spans="1:5" s="39" customFormat="1">
+      <c r="A53" s="36" t="s">
+        <v>219</v>
+      </c>
+      <c r="B53" s="37"/>
+      <c r="C53" s="38"/>
+      <c r="D53" s="38"/>
+      <c r="E53" s="38"/>
+    </row>
+    <row r="54" spans="1:5" s="24" customFormat="1" ht="351">
+      <c r="A54" s="19" t="s">
         <v>220</v>
       </c>
-      <c r="B46" s="37"/>
-      <c r="C46" s="38"/>
-      <c r="D46" s="38"/>
-      <c r="E46" s="38"/>
-    </row>
-    <row r="47" spans="1:5" s="24" customFormat="1" ht="216">
-      <c r="A47" s="19" t="s">
+      <c r="B54" s="22" t="s">
         <v>221</v>
       </c>
-      <c r="B47" s="22" t="s">
+      <c r="C54" s="25" t="s">
+        <v>230</v>
+      </c>
+      <c r="D54" s="12" t="s">
+        <v>229</v>
+      </c>
+      <c r="E54" s="12"/>
+    </row>
+    <row r="55" spans="1:5" s="24" customFormat="1">
+      <c r="A55" s="22"/>
+      <c r="B55" s="22"/>
+      <c r="C55" s="25" t="s">
         <v>222</v>
       </c>
-      <c r="C47" s="25" t="s">
+      <c r="D55" s="25" t="s">
         <v>223</v>
       </c>
-      <c r="D47" s="23" t="s">
-        <v>224</v>
-      </c>
-      <c r="E47" s="23"/>
-    </row>
-    <row r="48" spans="1:5" s="24" customFormat="1">
-      <c r="A48" s="22"/>
-      <c r="B48" s="22"/>
-      <c r="C48" s="25" t="s">
-        <v>223</v>
-      </c>
-      <c r="D48" s="25" t="s">
-        <v>225</v>
-      </c>
-      <c r="E48" s="23"/>
+      <c r="E55" s="23"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -3302,7 +3515,7 @@
   <sheetData>
     <row r="1" spans="1:5" s="34" customFormat="1">
       <c r="A1" s="33" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C1" s="35"/>
       <c r="D1" s="35"/>
@@ -3310,7 +3523,7 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="14" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C2" s="14"/>
       <c r="D2" s="14"/>
@@ -3318,260 +3531,260 @@
     </row>
     <row r="4" spans="1:5" s="34" customFormat="1">
       <c r="A4" s="33" t="s">
+        <v>197</v>
+      </c>
+      <c r="B4" s="34" t="s">
         <v>198</v>
       </c>
-      <c r="B4" s="34" t="s">
+      <c r="C4" s="35" t="s">
         <v>199</v>
-      </c>
-      <c r="C4" s="35" t="s">
-        <v>200</v>
       </c>
       <c r="D4" s="35" t="s">
         <v>93</v>
       </c>
       <c r="E4" s="35" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="5" spans="1:5" s="26" customFormat="1" ht="189">
       <c r="A5" s="27" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B5" s="26" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D5" s="27" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E5" s="27" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="7" spans="1:5" s="26" customFormat="1" ht="202.5">
       <c r="A7" s="27" t="s">
+        <v>109</v>
+      </c>
+      <c r="B7" s="26" t="s">
         <v>110</v>
       </c>
-      <c r="B7" s="26" t="s">
+      <c r="C7" s="27" t="s">
         <v>111</v>
       </c>
-      <c r="C7" s="27" t="s">
-        <v>112</v>
-      </c>
       <c r="D7" s="27" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E7" s="27" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="8" spans="1:5" s="26" customFormat="1" ht="409.5">
       <c r="A8" s="27"/>
       <c r="B8" s="26" t="s">
+        <v>119</v>
+      </c>
+      <c r="C8" s="27" t="s">
         <v>120</v>
       </c>
-      <c r="C8" s="27" t="s">
-        <v>121</v>
-      </c>
       <c r="D8" s="27" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E8" s="27" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="9" spans="1:5" s="26" customFormat="1" ht="216">
       <c r="A9" s="27"/>
       <c r="B9" s="26" t="s">
+        <v>112</v>
+      </c>
+      <c r="C9" s="27" t="s">
         <v>113</v>
       </c>
-      <c r="C9" s="27" t="s">
-        <v>114</v>
-      </c>
       <c r="D9" s="27" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E9" s="27" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="10" spans="1:5" s="26" customFormat="1">
       <c r="A10" s="27"/>
       <c r="B10" s="26" t="s">
+        <v>121</v>
+      </c>
+      <c r="C10" s="27" t="s">
         <v>122</v>
       </c>
-      <c r="C10" s="27" t="s">
-        <v>123</v>
-      </c>
       <c r="D10" s="27" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E10" s="27" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="11" spans="1:5" s="26" customFormat="1" ht="148.5">
       <c r="A11" s="27"/>
       <c r="B11" s="26" t="s">
+        <v>114</v>
+      </c>
+      <c r="C11" s="27" t="s">
         <v>115</v>
       </c>
-      <c r="C11" s="27" t="s">
-        <v>116</v>
-      </c>
       <c r="D11" s="27" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E11" s="27" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="13" spans="1:5" s="26" customFormat="1" ht="256.5">
       <c r="A13" s="27" t="s">
+        <v>116</v>
+      </c>
+      <c r="B13" s="26" t="s">
         <v>117</v>
       </c>
-      <c r="B13" s="26" t="s">
+      <c r="C13" s="27" t="s">
         <v>118</v>
       </c>
-      <c r="C13" s="27" t="s">
-        <v>119</v>
-      </c>
       <c r="D13" s="27" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E13" s="27" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="15" spans="1:5" s="26" customFormat="1" ht="108">
       <c r="A15" s="27" t="s">
+        <v>160</v>
+      </c>
+      <c r="B15" s="26" t="s">
+        <v>159</v>
+      </c>
+      <c r="C15" s="27" t="s">
         <v>161</v>
       </c>
-      <c r="B15" s="26" t="s">
-        <v>160</v>
-      </c>
-      <c r="C15" s="27" t="s">
-        <v>162</v>
-      </c>
       <c r="D15" s="27" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E15" s="27" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="17" spans="1:5" s="26" customFormat="1" ht="162">
       <c r="A17" s="27" t="s">
+        <v>127</v>
+      </c>
+      <c r="B17" s="26" t="s">
         <v>128</v>
       </c>
-      <c r="B17" s="26" t="s">
-        <v>129</v>
-      </c>
       <c r="C17" s="27" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D17" s="27" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E17" s="27" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="19" spans="1:5" s="26" customFormat="1" ht="409.5">
       <c r="A19" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="B19" s="26" t="s">
         <v>125</v>
       </c>
-      <c r="B19" s="26" t="s">
+      <c r="C19" s="27" t="s">
         <v>126</v>
       </c>
-      <c r="C19" s="27" t="s">
-        <v>127</v>
-      </c>
       <c r="D19" s="27" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E19" s="27" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="20" spans="1:5" s="26" customFormat="1">
       <c r="A20" s="27"/>
       <c r="C20" s="27" t="s">
+        <v>132</v>
+      </c>
+      <c r="D20" s="27" t="s">
         <v>133</v>
       </c>
-      <c r="D20" s="27" t="s">
-        <v>134</v>
-      </c>
       <c r="E20" s="27" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="21" spans="1:5" s="26" customFormat="1" ht="409.5">
       <c r="A21" s="27"/>
       <c r="C21" s="27" t="s">
+        <v>134</v>
+      </c>
+      <c r="D21" s="27" t="s">
         <v>135</v>
       </c>
-      <c r="D21" s="27" t="s">
-        <v>136</v>
-      </c>
       <c r="E21" s="27" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="22" spans="1:5" s="26" customFormat="1" ht="409.5">
       <c r="A22" s="27"/>
       <c r="C22" s="27" t="s">
+        <v>136</v>
+      </c>
+      <c r="D22" s="27" t="s">
         <v>137</v>
       </c>
-      <c r="D22" s="27" t="s">
-        <v>138</v>
-      </c>
       <c r="E22" s="27" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="23" spans="1:5" s="26" customFormat="1" ht="409.5">
       <c r="A23" s="27"/>
       <c r="C23" s="27" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D23" s="27" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E23" s="27"/>
     </row>
     <row r="24" spans="1:5" s="26" customFormat="1">
       <c r="A24" s="27"/>
       <c r="C24" s="27" t="s">
+        <v>149</v>
+      </c>
+      <c r="D24" s="27" t="s">
         <v>150</v>
       </c>
-      <c r="D24" s="27" t="s">
+      <c r="E24" s="27" t="s">
         <v>151</v>
-      </c>
-      <c r="E24" s="27" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="28" spans="1:5" s="26" customFormat="1" ht="409.5">
       <c r="A28" s="27" t="s">
+        <v>139</v>
+      </c>
+      <c r="B28" s="26" t="s">
         <v>140</v>
       </c>
-      <c r="B28" s="26" t="s">
+      <c r="C28" s="27" t="s">
         <v>141</v>
       </c>
-      <c r="C28" s="27" t="s">
+      <c r="D28" s="27" t="s">
         <v>142</v>
-      </c>
-      <c r="D28" s="27" t="s">
-        <v>143</v>
       </c>
       <c r="E28" s="27"/>
     </row>
     <row r="29" spans="1:5" s="26" customFormat="1">
       <c r="A29" s="27"/>
       <c r="C29" s="27" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D29" s="27"/>
       <c r="E29" s="27"/>
@@ -3579,66 +3792,66 @@
     <row r="30" spans="1:5" s="26" customFormat="1" ht="108">
       <c r="A30" s="27"/>
       <c r="C30" s="27" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D30" s="27" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E30" s="27" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="31" spans="1:5" s="26" customFormat="1" ht="81">
       <c r="A31" s="27"/>
       <c r="C31" s="27" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D31" s="27" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E31" s="27" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="32" spans="1:5" s="26" customFormat="1" ht="40.5">
       <c r="A32" s="27"/>
       <c r="C32" s="27" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D32" s="27" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E32" s="27" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="33" spans="1:5" s="26" customFormat="1" ht="40.5">
       <c r="A33" s="27"/>
       <c r="C33" s="27" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D33" s="27" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E33" s="27" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="37" spans="1:5" s="26" customFormat="1" ht="40.5">
       <c r="A37" s="27" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B37" s="26" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C37" s="27" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D37" s="27" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E37" s="27" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
   </sheetData>

--- a/internal_doc/03.开发设计/OM_Agent接口.xlsx
+++ b/internal_doc/03.开发设计/OM_Agent接口.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14385" windowHeight="7485" activeTab="2"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14385" windowHeight="7485" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="omagent需求（初稿）" sheetId="2" r:id="rId1"/>
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="235">
   <si>
     <t>检测host</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1822,6 +1822,10 @@
         }
     ]
 }</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{HostName:"",AgentPort:""} // 是否需要修改</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1920,7 +1924,67 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>{HostName:"",AgentPort:""} // 是否需要修改</t>
+    <t>$install remote agent</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>installRemoteAgent.js</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>var BUS_JSON =
+{
+    "HostInfo": [
+        {
+            "IP": "192.168.20.165", 
+            "HostName": "rhel64-test8", 
+            "User": "root", 
+            "Passwd": "sequoiadb", 
+            "SshPort": "22"
+        }
+    ]
+};
+var SYS_JSON =
+{
+    "ProgPath": "/opt/sequoiadb/bin/"
+};</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>{
+    "HostInfo": [
+        {
+            "errno": 0, 
+            "detail": "", 
+            "IsNeedUninstall": true, 
+            "AgentPort": "10000", 
+            "IP": "192.168.20.165"
+        }
+    ]
+}</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1928,7 +1992,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="14">
+  <fonts count="15">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2034,6 +2098,15 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -2134,7 +2207,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2233,6 +2306,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="3" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="20% - Accent3" xfId="3" builtinId="38"/>
@@ -3475,10 +3551,10 @@
         <v>221</v>
       </c>
       <c r="C54" s="25" t="s">
+        <v>229</v>
+      </c>
+      <c r="D54" s="12" t="s">
         <v>230</v>
-      </c>
-      <c r="D54" s="12" t="s">
-        <v>229</v>
       </c>
       <c r="E54" s="12"/>
     </row>
@@ -3502,7 +3578,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E37"/>
+  <dimension ref="A1:E38"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="18" style="13" customWidth="1"/>
@@ -3580,165 +3656,168 @@
         <v>203</v>
       </c>
     </row>
-    <row r="8" spans="1:5" s="26" customFormat="1" ht="409.5">
+    <row r="8" spans="1:5" s="26" customFormat="1" ht="216">
       <c r="A8" s="27"/>
       <c r="B8" s="26" t="s">
-        <v>119</v>
+        <v>231</v>
       </c>
       <c r="C8" s="27" t="s">
-        <v>120</v>
+        <v>232</v>
       </c>
       <c r="D8" s="27" t="s">
-        <v>205</v>
-      </c>
-      <c r="E8" s="27" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" s="26" customFormat="1" ht="216">
+        <v>233</v>
+      </c>
+      <c r="E8" s="40" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" s="26" customFormat="1" ht="409.5">
       <c r="A9" s="27"/>
       <c r="B9" s="26" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="D9" s="27" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E9" s="27" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" s="26" customFormat="1">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" s="26" customFormat="1" ht="216">
       <c r="A10" s="27"/>
       <c r="B10" s="26" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="C10" s="27" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="D10" s="27" t="s">
-        <v>122</v>
+        <v>207</v>
       </c>
       <c r="E10" s="27" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" s="26" customFormat="1" ht="148.5">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" s="26" customFormat="1">
       <c r="A11" s="27"/>
       <c r="B11" s="26" t="s">
+        <v>121</v>
+      </c>
+      <c r="C11" s="27" t="s">
+        <v>122</v>
+      </c>
+      <c r="D11" s="27" t="s">
+        <v>122</v>
+      </c>
+      <c r="E11" s="27" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" s="26" customFormat="1" ht="148.5">
+      <c r="A12" s="27"/>
+      <c r="B12" s="26" t="s">
         <v>114</v>
       </c>
-      <c r="C11" s="27" t="s">
+      <c r="C12" s="27" t="s">
         <v>115</v>
       </c>
-      <c r="D11" s="27" t="s">
+      <c r="D12" s="27" t="s">
         <v>206</v>
       </c>
-      <c r="E11" s="27" t="s">
+      <c r="E12" s="27" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="13" spans="1:5" s="26" customFormat="1" ht="256.5">
-      <c r="A13" s="27" t="s">
+    <row r="14" spans="1:5" s="26" customFormat="1" ht="256.5">
+      <c r="A14" s="27" t="s">
         <v>116</v>
       </c>
-      <c r="B13" s="26" t="s">
+      <c r="B14" s="26" t="s">
         <v>117</v>
       </c>
-      <c r="C13" s="27" t="s">
+      <c r="C14" s="27" t="s">
         <v>118</v>
       </c>
-      <c r="D13" s="27" t="s">
+      <c r="D14" s="27" t="s">
         <v>158</v>
       </c>
-      <c r="E13" s="27" t="s">
+      <c r="E14" s="27" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="15" spans="1:5" s="26" customFormat="1" ht="108">
-      <c r="A15" s="27" t="s">
+    <row r="16" spans="1:5" s="26" customFormat="1" ht="108">
+      <c r="A16" s="27" t="s">
         <v>160</v>
       </c>
-      <c r="B15" s="26" t="s">
+      <c r="B16" s="26" t="s">
         <v>159</v>
       </c>
-      <c r="C15" s="27" t="s">
+      <c r="C16" s="27" t="s">
         <v>161</v>
       </c>
-      <c r="D15" s="27" t="s">
+      <c r="D16" s="27" t="s">
         <v>163</v>
       </c>
-      <c r="E15" s="27" t="s">
+      <c r="E16" s="27" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="17" spans="1:5" s="26" customFormat="1" ht="162">
-      <c r="A17" s="27" t="s">
+    <row r="18" spans="1:5" s="26" customFormat="1" ht="162">
+      <c r="A18" s="27" t="s">
         <v>127</v>
       </c>
-      <c r="B17" s="26" t="s">
+      <c r="B18" s="26" t="s">
         <v>128</v>
       </c>
-      <c r="C17" s="27" t="s">
+      <c r="C18" s="27" t="s">
         <v>131</v>
       </c>
-      <c r="D17" s="27" t="s">
+      <c r="D18" s="27" t="s">
         <v>157</v>
       </c>
-      <c r="E17" s="27" t="s">
+      <c r="E18" s="27" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="19" spans="1:5" s="26" customFormat="1" ht="409.5">
-      <c r="A19" s="27" t="s">
+    <row r="20" spans="1:5" s="26" customFormat="1" ht="409.5">
+      <c r="A20" s="27" t="s">
         <v>124</v>
       </c>
-      <c r="B19" s="26" t="s">
+      <c r="B20" s="26" t="s">
         <v>125</v>
       </c>
-      <c r="C19" s="27" t="s">
+      <c r="C20" s="27" t="s">
         <v>126</v>
       </c>
-      <c r="D19" s="27" t="s">
+      <c r="D20" s="27" t="s">
         <v>215</v>
       </c>
-      <c r="E19" s="27" t="s">
+      <c r="E20" s="27" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="20" spans="1:5" s="26" customFormat="1">
-      <c r="A20" s="27"/>
-      <c r="C20" s="27" t="s">
-        <v>132</v>
-      </c>
-      <c r="D20" s="27" t="s">
-        <v>133</v>
-      </c>
-      <c r="E20" s="27" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" s="26" customFormat="1" ht="409.5">
+    <row r="21" spans="1:5" s="26" customFormat="1">
       <c r="A21" s="27"/>
       <c r="C21" s="27" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D21" s="27" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E21" s="27" t="s">
-        <v>151</v>
+        <v>213</v>
       </c>
     </row>
     <row r="22" spans="1:5" s="26" customFormat="1" ht="409.5">
       <c r="A22" s="27"/>
       <c r="C22" s="27" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D22" s="27" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E22" s="27" t="s">
         <v>151</v>
@@ -3747,79 +3826,79 @@
     <row r="23" spans="1:5" s="26" customFormat="1" ht="409.5">
       <c r="A23" s="27"/>
       <c r="C23" s="27" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D23" s="27" t="s">
-        <v>216</v>
-      </c>
-      <c r="E23" s="27"/>
-    </row>
-    <row r="24" spans="1:5" s="26" customFormat="1">
+        <v>137</v>
+      </c>
+      <c r="E23" s="27" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" s="26" customFormat="1" ht="409.5">
       <c r="A24" s="27"/>
       <c r="C24" s="27" t="s">
+        <v>138</v>
+      </c>
+      <c r="D24" s="27" t="s">
+        <v>216</v>
+      </c>
+      <c r="E24" s="27"/>
+    </row>
+    <row r="25" spans="1:5" s="26" customFormat="1">
+      <c r="A25" s="27"/>
+      <c r="C25" s="27" t="s">
         <v>149</v>
       </c>
-      <c r="D24" s="27" t="s">
+      <c r="D25" s="27" t="s">
         <v>150</v>
       </c>
-      <c r="E24" s="27" t="s">
+      <c r="E25" s="27" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="28" spans="1:5" s="26" customFormat="1" ht="409.5">
-      <c r="A28" s="27" t="s">
+    <row r="29" spans="1:5" s="26" customFormat="1" ht="409.5">
+      <c r="A29" s="27" t="s">
         <v>139</v>
       </c>
-      <c r="B28" s="26" t="s">
+      <c r="B29" s="26" t="s">
         <v>140</v>
       </c>
-      <c r="C28" s="27" t="s">
+      <c r="C29" s="27" t="s">
         <v>141</v>
       </c>
-      <c r="D28" s="27" t="s">
+      <c r="D29" s="27" t="s">
         <v>142</v>
       </c>
-      <c r="E28" s="27"/>
-    </row>
-    <row r="29" spans="1:5" s="26" customFormat="1">
-      <c r="A29" s="27"/>
-      <c r="C29" s="27" t="s">
-        <v>153</v>
-      </c>
-      <c r="D29" s="27"/>
       <c r="E29" s="27"/>
     </row>
-    <row r="30" spans="1:5" s="26" customFormat="1" ht="108">
+    <row r="30" spans="1:5" s="26" customFormat="1">
       <c r="A30" s="27"/>
       <c r="C30" s="27" t="s">
-        <v>132</v>
-      </c>
-      <c r="D30" s="27" t="s">
-        <v>209</v>
-      </c>
-      <c r="E30" s="27" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" s="26" customFormat="1" ht="81">
+        <v>153</v>
+      </c>
+      <c r="D30" s="27"/>
+      <c r="E30" s="27"/>
+    </row>
+    <row r="31" spans="1:5" s="26" customFormat="1" ht="108">
       <c r="A31" s="27"/>
       <c r="C31" s="27" t="s">
-        <v>154</v>
+        <v>132</v>
       </c>
       <c r="D31" s="27" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E31" s="27" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" s="26" customFormat="1" ht="40.5">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" s="26" customFormat="1" ht="81">
       <c r="A32" s="27"/>
       <c r="C32" s="27" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D32" s="27" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E32" s="27" t="s">
         <v>151</v>
@@ -3828,34 +3907,47 @@
     <row r="33" spans="1:5" s="26" customFormat="1" ht="40.5">
       <c r="A33" s="27"/>
       <c r="C33" s="27" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D33" s="27" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E33" s="27" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="37" spans="1:5" s="26" customFormat="1" ht="40.5">
-      <c r="A37" s="27" t="s">
+    <row r="34" spans="1:5" s="26" customFormat="1" ht="40.5">
+      <c r="A34" s="27"/>
+      <c r="C34" s="27" t="s">
+        <v>156</v>
+      </c>
+      <c r="D34" s="27" t="s">
+        <v>212</v>
+      </c>
+      <c r="E34" s="27" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" s="26" customFormat="1" ht="40.5">
+      <c r="A38" s="27" t="s">
         <v>152</v>
       </c>
-      <c r="B37" s="26" t="s">
+      <c r="B38" s="26" t="s">
         <v>123</v>
       </c>
-      <c r="C37" s="27" t="s">
+      <c r="C38" s="27" t="s">
         <v>122</v>
       </c>
-      <c r="D37" s="27" t="s">
+      <c r="D38" s="27" t="s">
         <v>122</v>
       </c>
-      <c r="E37" s="27" t="s">
+      <c r="E38" s="27" t="s">
         <v>122</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>